--- a/data/review/audit_T2.xlsx
+++ b/data/review/audit_T2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R122"/>
+  <dimension ref="A1:S126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,15 +494,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>audit</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>audit_note</t>
         </is>
@@ -571,6 +576,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -639,6 +645,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -703,6 +710,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -775,6 +783,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,7 +798,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Khi một tổ chức chuyển giao hoặc tự xử lý chất thải rắn thông thường sai quy định với khối lượng thuộc khung cao nhất, những hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?</t>
+          <t>Một cá nhân chuyển giao, chôn lấp hoặc thải trái quy định từ 5.000 kg đến dưới 10.000 kg chất thải rắn thông thường thì những loại chất thải và hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -829,28 +838,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Câu hỏi nói 'khối lượng thuộc khung cao nhất' nhưng điểm e (5.000 đến dưới 10.000 kg) không phải khung cao nhất (còn điểm g–l tới 150 triệu); ngoài ra câu hỏi đặt chủ thể là tổ chức trong khi mức 25–30 triệu là của cá nhân; tổ chức bị phạt gấp 02 lần (Điều 5 khoản 1 155/2016/NĐ-CP, đã đối chiếu)</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>l) Phạt tiền từ 100.000.000 đồng đến 150.000.000 đồng đối với trường hợp chuyển giao, cho, bán, tiếp nhận, chô...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi một tổ chức chuyển giao hoặc tự xử lý chất thải rắn thông thường sai quy định với khối lượng thuộc khung cao nhất, những hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi nói 'khối lượng thuộc khung cao nhất' nhưng điểm e (5.000 đến dưới 10.000 kg) không phải khung cao nhất (còn điểm g–l tới 150 triệu); ngoài ra câu hỏi đặt chủ thể là tổ chức trong khi mức 25–30 triệu là của cá nhân; tổ chức bị phạt gấp 02 lần (Điều 5 khoản 1 155/2016/NĐ-CP, đã đối chiếu)). Câu hỏi đặt chủ thể cá nhân (mức trong Điều là cho cá nhân, tổ chức gấp 02 lần theo khoản 1 Điều 5) và hỏi loại chất thải, hành vi, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -865,7 +867,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khi một tổ chức chuyển giao hoặc tự xử lý chất thải rắn thông thường sai quy định với khối lượng thuộc khung cao nhất, những hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?</t>
+          <t>Một cá nhân chuyển giao, chôn lấp hoặc thải trái quy định từ 5.000 kg đến dưới 10.000 kg chất thải rắn thông thường thì những loại chất thải và hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -905,28 +907,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Câu hỏi nói 'khối lượng thuộc khung cao nhất' nhưng điểm e (5.000 đến dưới 10.000 kg) không phải khung cao nhất (còn điểm g–l tới 150 triệu); ngoài ra câu hỏi đặt chủ thể là tổ chức trong khi mức 25–30 triệu là của cá nhân; tổ chức bị phạt gấp 02 lần (Điều 5 khoản 1 155/2016/NĐ-CP, đã đối chiếu)</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>l) Phạt tiền từ 100.000.000 đồng đến 150.000.000 đồng đối với trường hợp chuyển giao, cho, bán, tiếp nhận, chô...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi một tổ chức chuyển giao hoặc tự xử lý chất thải rắn thông thường sai quy định với khối lượng thuộc khung cao nhất, những hành vi nào bị phạt tiền từ 25.000.000 đồng đến 30.000.000 đồng?»; nhãn cũ khong_dat unanswerable_as_asked: Câu hỏi nói 'khối lượng thuộc khung cao nhất' nhưng điểm e (5.000 đến dưới 10.000 kg) không phải khung cao nhất (còn điểm g–l tới 150 triệu); ngoài ra câu hỏi đặt chủ thể là tổ chức trong khi mức 25–30 triệu là của cá nhân; tổ chức bị phạt gấp 02 lần (Điều 5 khoản 1 155/2016/NĐ-CP, đã đối chiếu)). Câu hỏi đặt chủ thể cá nhân (mức trong Điều là cho cá nhân, tổ chức gấp 02 lần theo khoản 1 Điều 5) và hỏi loại chất thải, hành vi, chạm chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -991,6 +986,7 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1055,6 +1051,7 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1119,6 +1116,7 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1187,6 +1185,7 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1255,6 +1254,7 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1323,6 +1323,7 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1391,6 +1392,7 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1455,6 +1457,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1519,6 +1522,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1583,6 +1587,7 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1647,6 +1652,7 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1711,6 +1717,7 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1775,6 +1782,7 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1839,6 +1847,7 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1903,6 +1912,7 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1971,6 +1981,7 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1985,7 +1996,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Theo quy định về quản lý thuế, người nộp thuế thuộc diện gia hạn do khó khăn được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?</t>
+          <t>Nếu người nộp thuế khó khăn do chưa được ngân sách nhà nước thanh toán cho công trình xây dựng cơ bản, thì được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2025,28 +2036,21 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>'Thuộc diện gia hạn do khó khăn' không chỉ ra trường hợp nào của khoản 1; điểm a, b, d cũng quy định phạm vi và thời gian gia hạn cho các diện khác. Điểm c là diện chưa được ngân sách thanh toán vốn đầu tư xây dựng cơ bản</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>a) Người nộp thuế nêu tại điểm a khoản 1 Điều này được gia hạn số tiền thuế nợ tính đến thời điểm xảy ra thiên...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về quản lý thuế, người nộp thuế thuộc diện gia hạn do khó khăn được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?»; nhãn cũ khong_dat question_ambiguous: 'Thuộc diện gia hạn do khó khăn' không chỉ ra trường hợp nào của khoản 1; điểm a, b, d cũng quy định phạm vi và thời gian gia hạn cho các diện khác. Điểm c là diện chưa được ngân sách thanh toán vốn đầu tư xây dựng cơ bản). Câu hỏi chốt diện chưa được ngân sách thanh toán vốn xây dựng cơ bản (điểm c khoản 1)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Theo quy định về quản lý thuế, người nộp thuế thuộc diện gia hạn do khó khăn được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?</t>
+          <t>Nếu người nộp thuế khó khăn do chưa được ngân sách nhà nước thanh toán cho công trình xây dựng cơ bản, thì được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2101,28 +2105,21 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>'Thuộc diện gia hạn do khó khăn' không chỉ ra trường hợp nào của khoản 1; điểm a, b, d cũng quy định phạm vi và thời gian gia hạn cho các diện khác. Điểm c là diện chưa được ngân sách thanh toán vốn đầu tư xây dựng cơ bản</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>a) Người nộp thuế nêu tại điểm a khoản 1 Điều này được gia hạn số tiền thuế nợ tính đến thời điểm xảy ra thiên...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về quản lý thuế, người nộp thuế thuộc diện gia hạn do khó khăn được gia hạn số tiền thuế nợ trong phạm vi nào và thời gian gia hạn tối đa là bao lâu?»; nhãn cũ khong_dat question_ambiguous: 'Thuộc diện gia hạn do khó khăn' không chỉ ra trường hợp nào của khoản 1; điểm a, b, d cũng quy định phạm vi và thời gian gia hạn cho các diện khác. Điểm c là diện chưa được ngân sách thanh toán vốn đầu tư xây dựng cơ bản). Câu hỏi chốt diện chưa được ngân sách thanh toán vốn xây dựng cơ bản (điểm c khoản 1)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2184,9 +2181,14 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>loại lineage (unanswerable_as_asked): Ở phiên bản 2, điểm b chỉ ghi 500.000 đồng; việc có phân biệt cá nhân/tổ chức hay không nằm ở quy định chung về thẩm quyền của nghị định (tổ chức gấp 02 lần), không ở đáp án; nửa sau câu hỏi còn là dạng có/không</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2256,9 +2258,14 @@
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>loại lineage (unanswerable_as_asked): Ở phiên bản 2, điểm b chỉ ghi 500.000 đồng; việc có phân biệt cá nhân/tổ chức hay không nằm ở quy định chung về thẩm quyền của nghị định (tổ chức gấp 02 lần), không ở đáp án; nửa sau câu hỏi còn là dạng có/không</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2327,6 +2334,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2391,6 +2399,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2455,6 +2464,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2519,6 +2529,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2583,6 +2594,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2597,7 +2609,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trường hợp cơ quan có thẩm quyền kiểm tra việc chấp hành pháp luật về bảo vệ môi trường, quyết định kiểm tra phải được gửi cho đối tượng kiểm tra trong thời hạn nào và trường hợp nào được miễn gửi trước?</t>
+          <t>Sau khi quyết định kiểm tra việc chấp hành pháp luật về bảo vệ môi trường được ban hành, ai phải tiến hành kiểm tra, chậm nhất trong bao lâu, và việc không gửi trước quyết định cho đối tượng dựa trên những quy định pháp luật nào?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2637,24 +2649,21 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Hai phiên bản trả lời như nhau về thời hạn (05 ngày) và ngoại lệ (kiểm tra đột xuất không báo trước); chỗ đổi chỉ là bỏ một căn cứ dẫn chiếu và 'Trưởng đoàn' → 'Đoàn'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cơ quan có thẩm quyền kiểm tra việc chấp hành pháp luật về bảo vệ môi trường, quyết định kiểm tra phải được gửi cho đối tượng kiểm tra trong thời hạn nào và trường hợp nào được miễn gửi trước?»; nhãn cũ khong_dat group_mismatch: Hai phiên bản trả lời như nhau về thời hạn (05 ngày) và ngoại lệ (kiểm tra đột xuất không báo trước); chỗ đổi chỉ là bỏ một căn cứ dẫn chiếu và 'Trưởng đoàn' → 'Đoàn'). Câu hỏi nay chạm cả hai chỗ đổi: Trưởng đoàn → Đoàn, và bỏ căn cứ pháp luật về cảnh sát môi trường</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2669,7 +2678,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trường hợp cơ quan có thẩm quyền kiểm tra việc chấp hành pháp luật về bảo vệ môi trường, quyết định kiểm tra phải được gửi cho đối tượng kiểm tra trong thời hạn nào và trường hợp nào được miễn gửi trước?</t>
+          <t>Sau khi quyết định kiểm tra việc chấp hành pháp luật về bảo vệ môi trường được ban hành, ai phải tiến hành kiểm tra, chậm nhất trong bao lâu, và việc không gửi trước quyết định cho đối tượng dựa trên những quy định pháp luật nào?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2709,24 +2718,21 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Hai phiên bản trả lời như nhau về thời hạn (05 ngày) và ngoại lệ (kiểm tra đột xuất không báo trước); chỗ đổi chỉ là bỏ một căn cứ dẫn chiếu và 'Trưởng đoàn' → 'Đoàn'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cơ quan có thẩm quyền kiểm tra việc chấp hành pháp luật về bảo vệ môi trường, quyết định kiểm tra phải được gửi cho đối tượng kiểm tra trong thời hạn nào và trường hợp nào được miễn gửi trước?»; nhãn cũ khong_dat group_mismatch: Hai phiên bản trả lời như nhau về thời hạn (05 ngày) và ngoại lệ (kiểm tra đột xuất không báo trước); chỗ đổi chỉ là bỏ một căn cứ dẫn chiếu và 'Trưởng đoàn' → 'Đoàn'). Câu hỏi nay chạm cả hai chỗ đổi: Trưởng đoàn → Đoàn, và bỏ căn cứ pháp luật về cảnh sát môi trường</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2791,6 +2797,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2859,6 +2866,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2927,6 +2935,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2941,7 +2950,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực thú y, những hành vi nào liên quan đến việc đưa động vật, sản phẩm động vật nhập khẩu đi gia công, chế biến bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?</t>
+          <t>Trong lĩnh vực kiểm dịch động vật, sản phẩm động vật nhập khẩu, những hành vi vi phạm quy định chung nào bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2981,24 +2990,21 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Câu hỏi chỉ hỏi hành vi đưa hàng nhập khẩu đi gia công, chế biến; ở cả hai mốc đó đều là cùng một hành vi, cùng mức 6–7 triệu (chỗ đổi là thêm điểm b–d về nhãn bao bì, câu hỏi không chạm tới)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực thú y, những hành vi nào liên quan đến việc đưa động vật, sản phẩm động vật nhập khẩu đi gia công, chế biến bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?»; nhãn cũ khong_dat group_mismatch: Câu hỏi chỉ hỏi hành vi đưa hàng nhập khẩu đi gia công, chế biến; ở cả hai mốc đó đều là cùng một hành vi, cùng mức 6–7 triệu (chỗ đổi là thêm điểm b–d về nhãn bao bì, câu hỏi không chạm tới)). Câu hỏi hỏi mọi hành vi bị phạt 6–7 triệu nên chạm chỗ thêm điểm b–d</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3013,7 +3019,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực thú y, những hành vi nào liên quan đến việc đưa động vật, sản phẩm động vật nhập khẩu đi gia công, chế biến bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?</t>
+          <t>Trong lĩnh vực kiểm dịch động vật, sản phẩm động vật nhập khẩu, những hành vi vi phạm quy định chung nào bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3053,24 +3059,21 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Câu hỏi chỉ hỏi hành vi đưa hàng nhập khẩu đi gia công, chế biến; ở cả hai mốc đó đều là cùng một hành vi, cùng mức 6–7 triệu (chỗ đổi là thêm điểm b–d về nhãn bao bì, câu hỏi không chạm tới)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trong lĩnh vực thú y, những hành vi nào liên quan đến việc đưa động vật, sản phẩm động vật nhập khẩu đi gia công, chế biến bị phạt tiền từ 6.000.000 đồng đến 7.000.000 đồng?»; nhãn cũ khong_dat group_mismatch: Câu hỏi chỉ hỏi hành vi đưa hàng nhập khẩu đi gia công, chế biến; ở cả hai mốc đó đều là cùng một hành vi, cùng mức 6–7 triệu (chỗ đổi là thêm điểm b–d về nhãn bao bì, câu hỏi không chạm tới)). Câu hỏi hỏi mọi hành vi bị phạt 6–7 triệu nên chạm chỗ thêm điểm b–d</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3135,6 +3138,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3199,6 +3203,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3263,6 +3268,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3331,6 +3337,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3399,6 +3406,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3467,6 +3475,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3528,9 +3537,14 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>loại lineage (gold_wrong): Văn bản nguồn (HTML gốc của 116/2015/NĐ-CP sửa điểm b) bị cắt ở '…cho các nhà đầu tư do' — thiếu chủ thể quyết định tỷ lệ; đáp án phiên bản 2 không đủ để trả lời. Cần bổ sung văn bản từ nguồn khác hoặc bỏ dòng</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3604,9 +3618,14 @@
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>loại lineage (gold_wrong): Văn bản nguồn (HTML gốc của 116/2015/NĐ-CP sửa điểm b) bị cắt ở '…cho các nhà đầu tư do' — thiếu chủ thể quyết định tỷ lệ; đáp án phiên bản 2 không đủ để trả lời. Cần bổ sung văn bản từ nguồn khác hoặc bỏ dòng</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3671,6 +3690,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3735,6 +3755,7 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3799,6 +3820,7 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3863,6 +3885,7 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3927,6 +3950,7 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3941,7 +3965,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hình thức xử phạt bổ sung tịch thu trong hoạt động thủy sản được xác định ra sao về đối tượng bị tịch thu?</t>
+          <t>Đối với các hành vi vi phạm quy định về sử dụng điện để khai thác thủy sản, hình thức xử phạt bổ sung tịch thu được áp dụng đối với những gì?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3981,24 +4005,21 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Câu hỏi không nêu hành vi; nhiều Điều khác của 103/2013/NĐ-CP cũng có khoản 'Hình thức xử phạt bổ sung' với điểm tịch thu riêng. Điều 15 là nhóm hành vi dùng kích điện, điện lưới khai thác thủy sản</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Hình thức xử phạt bổ sung tịch thu trong hoạt động thủy sản được xác định ra sao về đối tượng bị tịch thu?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu hành vi; nhiều Điều khác của 103/2013/NĐ-CP cũng có khoản 'Hình thức xử phạt bổ sung' với điểm tịch thu riêng. Điều 15 là nhóm hành vi dùng kích điện, điện lưới khai thác thủy sản). Câu hỏi nêu nhóm hành vi dùng điện khai thác thủy sản (Điều 15)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4013,7 +4034,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hình thức xử phạt bổ sung tịch thu trong hoạt động thủy sản được xác định ra sao về đối tượng bị tịch thu?</t>
+          <t>Đối với các hành vi vi phạm quy định về sử dụng điện để khai thác thủy sản, hình thức xử phạt bổ sung tịch thu được áp dụng đối với những gì?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4053,24 +4074,21 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Câu hỏi không nêu hành vi; nhiều Điều khác của 103/2013/NĐ-CP cũng có khoản 'Hình thức xử phạt bổ sung' với điểm tịch thu riêng. Điều 15 là nhóm hành vi dùng kích điện, điện lưới khai thác thủy sản</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Hình thức xử phạt bổ sung tịch thu trong hoạt động thủy sản được xác định ra sao về đối tượng bị tịch thu?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi không nêu hành vi; nhiều Điều khác của 103/2013/NĐ-CP cũng có khoản 'Hình thức xử phạt bổ sung' với điểm tịch thu riêng. Điều 15 là nhóm hành vi dùng kích điện, điện lưới khai thác thủy sản). Câu hỏi nêu nhóm hành vi dùng điện khai thác thủy sản (Điều 15)</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4135,6 +4153,7 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4199,6 +4218,7 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4213,7 +4233,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Theo quy định về đại lý làm thủ tục hải quan, những hành vi sử dụng mã số nhân viên đại lý sai quy định nào dẫn đến bị thu hồi mã số?</t>
+          <t>Theo quy định về đại lý làm thủ tục hải quan, những hành vi cho người khác sử dụng hoặc sử dụng mã số, hồ sơ không phải của chính mình nào dẫn đến việc thu hồi mã số nhân viên đại lý?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4253,28 +4273,21 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Điểm e (sử dụng mã số đã hết thời hạn hiệu lực) cũng là hành vi sử dụng mã số sai quy định dẫn đến thu hồi</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>e) Nhân viên đại lý làm thủ tục hải quan sử dụng mã số đã hết thời hạn hiệu lực để làm thủ tục hải quan.</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về đại lý làm thủ tục hải quan, những hành vi sử dụng mã số nhân viên đại lý sai quy định nào dẫn đến bị thu hồi mã số?»; nhãn cũ khong_dat question_ambiguous: Điểm e (sử dụng mã số đã hết thời hạn hiệu lực) cũng là hành vi sử dụng mã số sai quy định dẫn đến thu hồi). Câu hỏi chốt mã số, hồ sơ không phải của chính mình, loại điểm e (mã số hết hạn)</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4289,7 +4302,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Theo quy định về đại lý làm thủ tục hải quan, những hành vi sử dụng mã số nhân viên đại lý sai quy định nào dẫn đến bị thu hồi mã số?</t>
+          <t>Theo quy định về đại lý làm thủ tục hải quan, những hành vi cho người khác sử dụng hoặc sử dụng mã số, hồ sơ không phải của chính mình nào dẫn đến việc thu hồi mã số nhân viên đại lý?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4329,28 +4342,21 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Điểm e (sử dụng mã số đã hết thời hạn hiệu lực) cũng là hành vi sử dụng mã số sai quy định dẫn đến thu hồi</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>e) Nhân viên đại lý làm thủ tục hải quan sử dụng mã số đã hết thời hạn hiệu lực để làm thủ tục hải quan.</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về đại lý làm thủ tục hải quan, những hành vi sử dụng mã số nhân viên đại lý sai quy định nào dẫn đến bị thu hồi mã số?»; nhãn cũ khong_dat question_ambiguous: Điểm e (sử dụng mã số đã hết thời hạn hiệu lực) cũng là hành vi sử dụng mã số sai quy định dẫn đến thu hồi). Câu hỏi chốt mã số, hồ sơ không phải của chính mình, loại điểm e (mã số hết hạn)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4415,6 +4421,7 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4479,6 +4486,7 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4543,6 +4551,7 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4607,6 +4616,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4675,6 +4685,7 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4743,6 +4754,7 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4807,6 +4819,7 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4821,7 +4834,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Một tổ chức tín dụng mua nợ thì việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro liên quan đến khoản mua nợ được thực hiện như thế nào?</t>
+          <t>Khi tổ chức tín dụng mua nợ, việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro được áp dụng đối với đối tượng nào?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4861,24 +4874,21 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Cả hai phiên bản đều chỉ dẫn chiếu 'theo quy định của pháp luật'; chỗ đổi (khoản nợ đã mua → số tiền mua nợ) bị câu hỏi gộp thành 'khoản mua nợ' nên câu trả lời hai mốc như nhau</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức tín dụng mua nợ thì việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro liên quan đến khoản mua nợ được thực hiện như thế nào?»; nhãn cũ khong_dat group_mismatch: Cả hai phiên bản đều chỉ dẫn chiếu 'theo quy định của pháp luật'; chỗ đổi (khoản nợ đã mua → số tiền mua nợ) bị câu hỏi gộp thành 'khoản mua nợ' nên câu trả lời hai mốc như nhau). Câu hỏi hỏi đối tượng áp dụng, chính là chỗ đổi</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4893,7 +4903,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Một tổ chức tín dụng mua nợ thì việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro liên quan đến khoản mua nợ được thực hiện như thế nào?</t>
+          <t>Khi tổ chức tín dụng mua nợ, việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro được áp dụng đối với đối tượng nào?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4933,24 +4943,21 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Cả hai phiên bản đều chỉ dẫn chiếu 'theo quy định của pháp luật'; chỗ đổi (khoản nợ đã mua → số tiền mua nợ) bị câu hỏi gộp thành 'khoản mua nợ' nên câu trả lời hai mốc như nhau</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một tổ chức tín dụng mua nợ thì việc phân loại nợ, trích lập và sử dụng dự phòng rủi ro liên quan đến khoản mua nợ được thực hiện như thế nào?»; nhãn cũ khong_dat group_mismatch: Cả hai phiên bản đều chỉ dẫn chiếu 'theo quy định của pháp luật'; chỗ đổi (khoản nợ đã mua → số tiền mua nợ) bị câu hỏi gộp thành 'khoản mua nợ' nên câu trả lời hai mốc như nhau). Câu hỏi hỏi đối tượng áp dụng, chính là chỗ đổi</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4965,7 +4972,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Một chủ rừng là tổ chức lập phương án quản lý rừng bền vững thì cơ quan nào có thẩm quyền phê duyệt phương án và thẩm quyền đó có bao gồm việc điều chỉnh không?</t>
+          <t>Một ban quản lý rừng phòng hộ thuộc địa phương lập phương án quản lý rừng bền vững thì phương án do cơ quan nào phê duyệt và cơ quan đó có những thẩm quyền gì đối với phương án?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5005,28 +5012,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Câu hỏi bỏ mất điều kiện ở tên Điều 13 (chủ rừng là tổ chức không thuộc đối tượng Điều 11 và Điều 12); chủ rừng là tổ chức thuộc Điều 11, 12 có cơ quan phê duyệt khác</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Điều 13. Phê duyệt phương án quản lý rừng bền vững của chủ rừng là tổ chức không thuộc đối tượng quy định tại Điều 11 và khoản 1 Điều 12</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một chủ rừng là tổ chức lập phương án quản lý rừng bền vững thì cơ quan nào có thẩm quyền phê duyệt phương án và thẩm quyền đó có bao gồm việc điều chỉnh không?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi bỏ mất điều kiện ở tên Điều 13 (chủ rừng là tổ chức không thuộc đối tượng Điều 11 và Điều 12); chủ rừng là tổ chức thuộc Điều 11, 12 có cơ quan phê duyệt khác). Câu hỏi nêu ban quản lý rừng phòng hộ thuộc địa phương (không thuộc Điều 11, 12) và hỏi thẩm quyền, chạm chỗ thêm 'điều chỉnh'</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Một chủ rừng là tổ chức lập phương án quản lý rừng bền vững thì cơ quan nào có thẩm quyền phê duyệt phương án và thẩm quyền đó có bao gồm việc điều chỉnh không?</t>
+          <t>Một ban quản lý rừng phòng hộ thuộc địa phương lập phương án quản lý rừng bền vững thì phương án do cơ quan nào phê duyệt và cơ quan đó có những thẩm quyền gì đối với phương án?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5081,33 +5081,26 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Câu hỏi bỏ mất điều kiện ở tên Điều 13 (chủ rừng là tổ chức không thuộc đối tượng Điều 11 và Điều 12); chủ rừng là tổ chức thuộc Điều 11, 12 có cơ quan phê duyệt khác</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Điều 13. Phê duyệt phương án quản lý rừng bền vững của chủ rừng là tổ chức không thuộc đối tượng quy định tại Điều 11 và khoản 1 Điều 12</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một chủ rừng là tổ chức lập phương án quản lý rừng bền vững thì cơ quan nào có thẩm quyền phê duyệt phương án và thẩm quyền đó có bao gồm việc điều chỉnh không?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi bỏ mất điều kiện ở tên Điều 13 (chủ rừng là tổ chức không thuộc đối tượng Điều 11 và Điều 12); chủ rừng là tổ chức thuộc Điều 11, 12 có cơ quan phê duyệt khác). Câu hỏi nêu ban quản lý rừng phòng hộ thuộc địa phương (không thuộc Điều 11, 12) và hỏi thẩm quyền, chạm chỗ thêm 'điều chỉnh'</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:a8ca4f44-eb7f-11f0-b54c-8b73b0357750:2023-08-15</t>
+          <t>vilextime:T2:provision:a324f196-df4c-11f0-8fa5-81d0733a4bb5:2024-01-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5117,37 +5110,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pháp luật về đăng kiểm tàu biển quy định phạm vi các loại giấy chứng nhận mà tổ chức đăng kiểm nước ngoài được ủy quyền cấp cho tàu biển Việt Nam như thế nào?</t>
+          <t>Bộ tiêu chí dùng để đánh giá quản lý rừng bền vững có bao nhiêu nguyên tắc, tiêu chí và chỉ số?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Điều 13. Nguyên tắc thực hiện ủy quyền cho tổ chức đăng kiểm nước ngoài kiểm định, phân cấp và cấp giấy chứng nhận an toàn kỹ thuật về an toàn hàng hải, an ninh tàu biển, điều kiện bảo đảm lao động hàng hải và phòng ngừa ô nhiễm môi trường cho tàu biển Việt Nam</t>
+          <t>VÀ CHỨNG CHỈ QUẢN LÝ RỪNG BỀN VỮNG</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1. Bộ trưởng Bộ Giao thông vận tải giao Cục trưởng Cục Đăng kiểm Việt Nam thực hiện ủy quyền cho tổ chức đăng kiểm nước ngoài kiểm định, phân cấp và cấp giấy chứng nhận kỹ thuật về an toàn hàng hải, an ninh tàu biển, điều kiện bảo đảm lao động hàng hải và phòng ngừa ô nhiễm môi trường cho tàu biển Việt Nam.</t>
+          <t>Bộ tiêu chí quản lý rừng bền vững gồm 07 nguyên tắc, 34 tiêu chí và 122 chỉ số. Chi tiết Bộ tiêu chí quản lý rừng bền vững theo quy định tại Phụ lục I kèm theo Thông tư này.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 13</t>
+          <t>Điều 14</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40/2016/TT-BGTVT</t>
+          <t>28/2018/TT-BNNPTNT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=116454</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5161,17 +5154,26 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lead_in_wrong</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Đáp án đúng; câu dẫn là mảnh tên Chương ('VÀ CHỨNG CHỈ QUẢN LÝ RỪNG BỀN VỮNG') và đáp án phiên bản 2 dính tên Điều 14</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:aaea5032-eb78-11f0-bce7-15d9ef15c2e3#k1:2011-01-31</t>
+          <t>vilextime:T2:provision:a324f196-df4c-11f0-8fa5-81d0733a4bb5:2024-02-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5181,37 +5183,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Khi xác định thẩm quyền xử phạt vi phạm hành chính trong hoạt động thương mại, nguyên tắc xác định thẩm quyền được thực hiện theo những văn bản nào?</t>
+          <t>Bộ tiêu chí dùng để đánh giá quản lý rừng bền vững có bao nhiêu nguyên tắc, tiêu chí và chỉ số?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2011-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Điều 61. Nguyên tắc xác định thẩm quyền xử phạt vi phạm hành chính và uỷ quyền xử phạt vi phạm hành chính</t>
+          <t>VÀ CHỨNG CHỈ QUẢN LÝ RỪNG BỀN VỮNG</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1. Nguyên tắc xác định thẩm quyền xử phạt vi phạm hành chính thực hiện theo quy định tại Điều 42 Pháp lệnh Xử lý vi phạm hành chính và Điều 13 Nghị định số 134/2003/NĐ-CP ngày 14 tháng 11 năm 2003 của Chính phủ quy định chi tiết thi hành một số điều của Pháp lệnh Xử lý vi phạm hành chính.</t>
+          <t>Điều 14. Tiêu chí quản lý rừng bền vững Bộ tiêu chí quản lý rừng bền vững gồm 07 nguyên tắc, 36 tiêu chí và 139 chỉ số. Chi tiết Bộ tiêu chí quản lý rừng bền vững theo quy định tại Phụ lục I ban hành kèm theo Thông tư này.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 61</t>
+          <t>Điều 14</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>06/2008/NĐ-CP</t>
+          <t>28/2018/TT-BNNPTNT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=11618</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133923</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5225,21 +5227,26 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lead_in_wrong</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Phiên bản 2 dùng tên viết tắt ('Pháp lệnh', 'Nghị định số 128') định nghĩa ở chỗ khác của văn bản</t>
+          <t>Đáp án đúng; câu dẫn là mảnh tên Chương ('VÀ CHỨNG CHỈ QUẢN LÝ RỪNG BỀN VỮNG') và đáp án phiên bản 2 dính tên Điều 14</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ad1f7f20-2c7e-11f1-a841-bdadd8e34925:2023-08-31</t>
+          <t>vilextime:T2:provision:a8ca4f44-eb7f-11f0-b54c-8b73b0357750:2023-08-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5249,37 +5256,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Khi một tổ chức tín dụng xây dựng quy định nội bộ về cho vay và quản lý tiền vay, quy định đó phải bao quát những nội dung gì?</t>
+          <t>Pháp luật về đăng kiểm tàu biển quy định phạm vi các loại giấy chứng nhận mà tổ chức đăng kiểm nước ngoài được ủy quyền cấp cho tàu biển Việt Nam như thế nào?</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Điều 22. Quy định nội bộ</t>
+          <t>Điều 13. Nguyên tắc thực hiện ủy quyền cho tổ chức đăng kiểm nước ngoài kiểm định, phân cấp và cấp giấy chứng nhận an toàn kỹ thuật về an toàn hàng hải, an ninh tàu biển, điều kiện bảo đảm lao động hàng hải và phòng ngừa ô nhiễm môi trường cho tàu biển Việt Nam</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1. Căn cứ quy định tại Luật các tổ chức tín dụng, Thông tư này và các quy định của pháp luật có liên quan, tổ chức tín dụng ban hành quy định nội bộ về cho vay, quản lý tiền vay phù hợp với đặc điểm hoạt động kinh doanh của tổ chức tín dụng (sau đây gọi là quy định nội bộ về cho vay).</t>
+          <t>1. Bộ trưởng Bộ Giao thông vận tải giao Cục trưởng Cục Đăng kiểm Việt Nam thực hiện ủy quyền cho tổ chức đăng kiểm nước ngoài kiểm định, phân cấp và cấp giấy chứng nhận kỹ thuật về an toàn hàng hải, an ninh tàu biển, điều kiện bảo đảm lao động hàng hải và phòng ngừa ô nhiễm môi trường cho tàu biển Việt Nam.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 22</t>
+          <t>Khoản 1 Điều 13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>39/2016/TT-NHNN</t>
+          <t>40/2016/TT-BGTVT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118230</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=116454</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5289,33 +5296,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Hỏi quy định nội bộ 'phải bao quát những nội dung gì' nhưng khoản 2 mới liệt kê nội dung tối thiểu; khoản 1 chỉ nói việc ban hành</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2. Quy định nội bộ về cho vay của tổ chức tín dụng được thực hiện trong toàn hệ thống và phải có tối thiểu các...</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ad1f7f20-2c7e-11f1-a841-bdadd8e34925:2023-09-01</t>
+          <t>vilextime:T2:provision:aaea5032-eb78-11f0-bce7-15d9ef15c2e3#k1:2011-01-31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5325,37 +5321,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Khi một tổ chức tín dụng xây dựng quy định nội bộ về cho vay và quản lý tiền vay, quy định đó phải bao quát những nội dung gì?</t>
+          <t>Khi xác định thẩm quyền xử phạt vi phạm hành chính trong hoạt động thương mại, nguyên tắc xác định thẩm quyền được thực hiện theo những văn bản nào?</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2011-01-31</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Điều 22. Quy định nội bộ</t>
+          <t>Điều 61. Nguyên tắc xác định thẩm quyền xử phạt vi phạm hành chính và uỷ quyền xử phạt vi phạm hành chính</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1. Căn cứ quy định tại Luật Các tổ chức tín dụng, Thông tư này và các quy định của pháp luật có liên quan, tổ chức tín dụng ban hành quy định nội bộ về cho vay, bao gồm quy định về cho vay bằng phương tiện điện tử (nếu có), quản lý tiền vay phù hợp với đặc điểm hoạt động kinh doanh của tổ chức tín dụng (sau đây gọi là quy định nội bộ về cho vay).</t>
+          <t>1. Nguyên tắc xác định thẩm quyền xử phạt vi phạm hành chính thực hiện theo quy định tại Điều 42 Pháp lệnh Xử lý vi phạm hành chính và Điều 13 Nghị định số 134/2003/NĐ-CP ngày 14 tháng 11 năm 2003 của Chính phủ quy định chi tiết thi hành một số điều của Pháp lệnh Xử lý vi phạm hành chính.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 22</t>
+          <t>Khoản 1 Điều 61</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>39/2016/TT-NHNN</t>
+          <t>06/2008/NĐ-CP</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118230</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=11618</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5365,33 +5361,26 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Hỏi quy định nội bộ 'phải bao quát những nội dung gì' nhưng khoản 2 mới liệt kê nội dung tối thiểu; khoản 1 chỉ nói việc ban hành</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>2. Quy định nội bộ về cho vay của tổ chức tín dụng được thực hiện trong toàn hệ thống và phải có tối thiểu các...</t>
-        </is>
-      </c>
+          <t>Phiên bản 2 dùng tên viết tắt ('Pháp lệnh', 'Nghị định số 128') định nghĩa ở chỗ khác của văn bản</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:b0219100-df52-11f0-8c76-6f8482bba0f2:2021-12-31</t>
+          <t>vilextime:T2:provision:ad1f7f20-2c7e-11f1-a841-bdadd8e34925:2023-08-31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5401,37 +5390,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nếu Công an cấp tỉnh xử lý vi phạm trong lĩnh vực văn hóa và quảng cáo, thì Giám đốc Công an cấp tỉnh được phạt tiền tối đa bao nhiêu ở mỗi lĩnh vực?</t>
+          <t>Khi ban hành quy định nội bộ về cho vay, tổ chức tín dụng phải căn cứ vào những văn bản nào và quy định nội bộ đó phải bao gồm những hoạt động gì?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5. Giám đốc Công an cấp tỉnh có quyền:</t>
+          <t>Điều 22. Quy định nội bộ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>b) Phạt tiền đến 25.000.000 đồng trong lĩnh vực văn hóa; phạt tiền đến 50.000.000 đồng trong lĩnh vực quảng cáo;</t>
+          <t>1. Căn cứ quy định tại Luật các tổ chức tín dụng, Thông tư này và các quy định của pháp luật có liên quan, tổ chức tín dụng ban hành quy định nội bộ về cho vay, quản lý tiền vay phù hợp với đặc điểm hoạt động kinh doanh của tổ chức tín dụng (sau đây gọi là quy định nội bộ về cho vay).</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 5 Điều 66</t>
+          <t>Khoản 1 Điều 22</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>38/2021/NĐ-CP</t>
+          <t>39/2016/TT-NHNN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147628</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118230</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5441,29 +5430,26 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi một tổ chức tín dụng xây dựng quy định nội bộ về cho vay và quản lý tiền vay, quy định đó phải bao quát những nội dung gì?»; nhãn cũ khong_dat question_ambiguous: Hỏi quy định nội bộ 'phải bao quát những nội dung gì' nhưng khoản 2 mới liệt kê nội dung tối thiểu; khoản 1 chỉ nói việc ban hành). Câu hỏi hỏi căn cứ và phạm vi quy định nội bộ theo khoản 1, không còn hỏi nội dung tối thiểu của khoản 2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:b0219100-df52-11f0-8c76-6f8482bba0f2:2022-01-01</t>
+          <t>vilextime:T2:provision:ad1f7f20-2c7e-11f1-a841-bdadd8e34925:2023-09-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5473,37 +5459,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nếu Công an cấp tỉnh xử lý vi phạm trong lĩnh vực văn hóa và quảng cáo, thì Giám đốc Công an cấp tỉnh được phạt tiền tối đa bao nhiêu ở mỗi lĩnh vực?</t>
+          <t>Khi ban hành quy định nội bộ về cho vay, tổ chức tín dụng phải căn cứ vào những văn bản nào và quy định nội bộ đó phải bao gồm những hoạt động gì?</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5. Giám đốc Công an cấp tỉnh có quyền:</t>
+          <t>Điều 22. Quy định nội bộ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>b) Phạt tiền đến 25.000.000 đồng đối với hành vi vi phạm hành chính trong lĩnh vực văn hóa; phạt tiền đến 50.000.000 đồng đối với hành vi vi phạm hành chính trong lĩnh vực quảng cáo;</t>
+          <t>1. Căn cứ quy định tại Luật Các tổ chức tín dụng, Thông tư này và các quy định của pháp luật có liên quan, tổ chức tín dụng ban hành quy định nội bộ về cho vay, bao gồm quy định về cho vay bằng phương tiện điện tử (nếu có), quản lý tiền vay phù hợp với đặc điểm hoạt động kinh doanh của tổ chức tín dụng (sau đây gọi là quy định nội bộ về cho vay).</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 5 Điều 66</t>
+          <t>Khoản 1 Điều 22</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>38/2021/NĐ-CP</t>
+          <t>39/2016/TT-NHNN</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147628</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118230</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5513,29 +5499,26 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi một tổ chức tín dụng xây dựng quy định nội bộ về cho vay và quản lý tiền vay, quy định đó phải bao quát những nội dung gì?»; nhãn cũ khong_dat question_ambiguous: Hỏi quy định nội bộ 'phải bao quát những nội dung gì' nhưng khoản 2 mới liệt kê nội dung tối thiểu; khoản 1 chỉ nói việc ban hành). Câu hỏi hỏi căn cứ và phạm vi quy định nội bộ theo khoản 1, không còn hỏi nội dung tối thiểu của khoản 2</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:b03f10b0-1f6f-11f1-9bef-dddd0e9eac84:2022-02-15</t>
+          <t>vilextime:T2:provision:ad521220-eae6-11f0-9d27-171cbacf1b6b:2025-12-15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5545,37 +5528,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Việc gửi biên bản chuyển giao quyền đại diện chủ sở hữu nhà nước sau khi SCIC hoàn tất tiếp nhận được xác định ra sao về nơi nhận?</t>
+          <t>Người nước ngoài bị trục xuất có nghĩa vụ gì đối với những nội dung ghi trong quyết định xử phạt trục xuất đã ban hành đối với mình?</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Điều 10. Trình tự chuyển giao</t>
+          <t>2. Nghĩa vụ của người bị trục xuất:</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>6. Khi hoàn tất việc chuyển giao, SCIC gửi Biên bản chuyển giao cho bên giao (01 bản), doanh nghiệp (01 bản) và Ủy ban Quản lý vốn nhà nước tại doanh nghiệp (01 bản).</t>
+          <t>a) Thực hiện đầy đủ các quy định ghi trong quyết định xử phạt vi phạm hành chính có áp dụng hình thức xử phạt trục xuất, trừ trường hợp quy định tại khoản 4 Điều 10 Nghị định này;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 10</t>
+          <t>Điểm a Khoản 2 Điều 7</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>83/2018/TT-BTC</t>
+          <t>142/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135990</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152993</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5595,11 +5578,12 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:b9258d90-2d47-11f1-b543-63b7caf8f3e3:2022-06-01</t>
+          <t>vilextime:T2:provision:b0219100-df52-11f0-8c76-6f8482bba0f2:2021-12-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5609,37 +5593,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực giáo dục nghề nghiệp, thủ tục giải thể cơ sở giáo dục nghề nghiệp được bắt đầu như thế nào và hồ sơ được xử lý ra sao?</t>
+          <t>Nếu Công an cấp tỉnh xử lý vi phạm trong lĩnh vực văn hóa và quảng cáo, thì Giám đốc Công an cấp tỉnh được phạt tiền tối đa bao nhiêu ở mỗi lĩnh vực?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4. Thủ tục, thẩm quyền giải thể, cho phép giải thể cơ sở giáo dục nghề nghiệp:</t>
+          <t>5. Giám đốc Công an cấp tỉnh có quyền:</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>a) Cơ quan, tổ chức, cá nhân đề nghị giải thể cơ sở giáo dục nghề nghiệp gửi hồ sơ theo quy định tại khoản 2, khoản 3 Điều này qua cổng dịch vụ công trực tuyến hoặc bưu chính hoặc trực tiếp đến cơ quan, tổ chức quy định tại các điểm b, c và d khoản 1 Điều 8 Nghị định này. Trong thời hạn 15 ngày làm việc kể từ ngày nhận được hồ sơ, cơ quan, tổ chức quy định tại các điểm b, c và d khoản 1 Điều 8 Nghị định này kiểm tra hồ sơ và trình người có thẩm quyền quy định tại điểm d khoản 4 Điều này quyết định giải thể, cho phép giải thể cơ sở giáo dục nghề nghiệp theo Mẫu số 03 Phụ lục III ban hành kèm theo Nghị định này. Trường hợp hồ sơ không hợp lệ hoặc không quyết định giải thể, cho phép giải thể thì có văn bản trả lời và nêu rõ lý do.</t>
+          <t>b) Phạt tiền đến 25.000.000 đồng trong lĩnh vực văn hóa; phạt tiền đến 50.000.000 đồng trong lĩnh vực quảng cáo;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 4 Điều 11</t>
+          <t>Điểm b Khoản 5 Điều 66</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>143/2016/NĐ-CP</t>
+          <t>38/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=114476</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147628</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5649,25 +5633,34 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Phiên bản 1 không nói cách nộp hồ sơ (bắt đầu thủ tục); chỉ có bước thẩm định 20 ngày</t>
+          <t>Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ba2dff42-eb6b-11f0-8be9-130a5f277e0a#k4:2017-12-31</t>
+          <t>vilextime:T2:provision:b0219100-df52-11f0-8c76-6f8482bba0f2:2022-01-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5677,37 +5670,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Một Cảng vụ hàng hải trong quá trình điều tra tai nạn hàng hải thì phải thông báo cho cơ quan điều tra và chuyển giao hồ sơ trong những trường hợp nào?</t>
+          <t>Nếu Công an cấp tỉnh xử lý vi phạm trong lĩnh vực văn hóa và quảng cáo, thì Giám đốc Công an cấp tỉnh được phạt tiền tối đa bao nhiêu ở mỗi lĩnh vực?</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2017-12-31</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Điều 12. Tổ chức điều tra tai nạn hàng hải</t>
+          <t>5. Giám đốc Công an cấp tỉnh có quyền:</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4. Trong quá trình điều tra tai nạn hàng hải, nếu phát hiện có dấu hiệu cấu thành tội phạm thì Giám đốc Cảng vụ hàng hải thông báo cho cơ quan điều tra có thẩm quyền và chuyển giao hồ sơ, tài liệu, vật chứng có liên quan đến vụ tai nạn hàng hải theo yêu cầu của cơ quan điều tra có thẩm quyền; trước khi chuyển giao, hồ sơ, tài liệu phải được sao y hoặc phô tô để lưu lại phục vụ việc điều tra tai nạn hàng hải; việc chuyển giao hồ sơ, tài liệu, vật chứng phải được lập thành biên bản bàn giao.</t>
+          <t>b) Phạt tiền đến 25.000.000 đồng đối với hành vi vi phạm hành chính trong lĩnh vực văn hóa; phạt tiền đến 50.000.000 đồng đối với hành vi vi phạm hành chính trong lĩnh vực quảng cáo;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 12</t>
+          <t>Điểm b Khoản 5 Điều 66</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>34/2015/TT-BGTVT</t>
+          <t>38/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92556</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147628</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5717,21 +5710,34 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Hai phiên bản cùng mức 25 triệu (văn hóa) và 50 triệu (quảng cáo); chỉ thêm chữ 'đối với hành vi vi phạm hành chính'</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:bdb195ee-df3f-11f0-a46b-f9e80158a78f:2025-06-22</t>
+          <t>vilextime:T2:provision:b03f10b0-1f6f-11f1-9bef-dddd0e9eac84:2022-02-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5741,37 +5747,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pháp luật về mở, đóng sân bay chuyên dùng quy định việc xử lý hồ sơ không hợp lệ như thế nào về cơ quan thông báo, hình thức và thời hạn?</t>
+          <t>Việc gửi biên bản chuyển giao quyền đại diện chủ sở hữu nhà nước sau khi SCIC hoàn tất tiếp nhận được xác định ra sao về nơi nhận?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2. Trình tự, thủ tục giải quyết:</t>
+          <t>Điều 10. Trình tự chuyển giao</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>b) Trường hợp hồ sơ không hợp lệ, trong thời hạn 05 ngày làm việc, Bộ Tổng Tham mưu có trách nhiệm thông báo bằng văn bản cho chủ sở hữu bãi cất, hạ cánh để hoàn thiện hồ sơ theo quy định;</t>
+          <t>6. Khi hoàn tất việc chuyển giao, SCIC gửi Biên bản chuyển giao cho bên giao (01 bản), doanh nghiệp (01 bản) và Ủy ban Quản lý vốn nhà nước tại doanh nghiệp (01 bản).</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 14</t>
+          <t>Khoản 6 Điều 10</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>42/2016/NĐ-CP</t>
+          <t>83/2018/TT-BTC</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135990</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5781,33 +5787,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Nghị định có cùng điểm b 'hồ sơ không hợp lệ … 05 ngày, Bộ Tổng Tham mưu thông báo' ở Điều 12 (đóng sân bay chuyên dùng), 14, 16 (đóng bãi cất hạ cánh), 17 (đóng tạm thời); câu hỏi không nêu thủ tục nào. Gold là Điều 14 (bãi cất, hạ cánh trên mặt đất)</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Điều 12 điểm b: Trường hợp hồ sơ không hợp lệ, trong thời hạn 05 ngày làm việc, Bộ Tổng Tham mưu có trách nhiệm thông báo bằng văn bản cho chủ sở hữu sân bay…</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:bdb195ee-df3f-11f0-a46b-f9e80158a78f:2025-06-23</t>
+          <t>vilextime:T2:provision:b9258d90-2d47-11f1-b543-63b7caf8f3e3:2022-06-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5817,37 +5812,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pháp luật về mở, đóng sân bay chuyên dùng quy định việc xử lý hồ sơ không hợp lệ như thế nào về cơ quan thông báo, hình thức và thời hạn?</t>
+          <t>Trong lĩnh vực giáo dục nghề nghiệp, thủ tục giải thể cơ sở giáo dục nghề nghiệp được bắt đầu như thế nào và hồ sơ được xử lý ra sao?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2. Trình tự, thủ tục giải quyết:</t>
+          <t>4. Thủ tục, thẩm quyền giải thể, cho phép giải thể cơ sở giáo dục nghề nghiệp:</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>b) Trường hợp hồ sơ không hợp lệ, trong thời hạn năm (05) ngày làm việc, kể từ ngày nhận hồ sơ, Cục Tác chiến, Bộ Tổng Tham mưu có văn bản điện tử yêu cầu chủ sở hữu bãi cất, hạ cánh hoàn thiện hồ sơ theo quy định;</t>
+          <t>a) Cơ quan, tổ chức, cá nhân đề nghị giải thể cơ sở giáo dục nghề nghiệp gửi hồ sơ theo quy định tại khoản 2, khoản 3 Điều này qua cổng dịch vụ công trực tuyến hoặc bưu chính hoặc trực tiếp đến cơ quan, tổ chức quy định tại các điểm b, c và d khoản 1 Điều 8 Nghị định này. Trong thời hạn 15 ngày làm việc kể từ ngày nhận được hồ sơ, cơ quan, tổ chức quy định tại các điểm b, c và d khoản 1 Điều 8 Nghị định này kiểm tra hồ sơ và trình người có thẩm quyền quy định tại điểm d khoản 4 Điều này quyết định giải thể, cho phép giải thể cơ sở giáo dục nghề nghiệp theo Mẫu số 03 Phụ lục III ban hành kèm theo Nghị định này. Trường hợp hồ sơ không hợp lệ hoặc không quyết định giải thể, cho phép giải thể thì có văn bản trả lời và nêu rõ lý do.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 2 Điều 14</t>
+          <t>Điểm a Khoản 4 Điều 11</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>42/2016/NĐ-CP</t>
+          <t>143/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=114476</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5857,33 +5852,26 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Nghị định có cùng điểm b 'hồ sơ không hợp lệ … 05 ngày, Bộ Tổng Tham mưu thông báo' ở Điều 12 (đóng sân bay chuyên dùng), 14, 16 (đóng bãi cất hạ cánh), 17 (đóng tạm thời); câu hỏi không nêu thủ tục nào. Gold là Điều 14 (bãi cất, hạ cánh trên mặt đất)</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Điều 12 điểm b: Trường hợp hồ sơ không hợp lệ, trong thời hạn 05 ngày làm việc, Bộ Tổng Tham mưu có trách nhiệm thông báo bằng văn bản cho chủ sở hữu sân bay…</t>
-        </is>
-      </c>
+          <t>Phiên bản 1 không nói cách nộp hồ sơ (bắt đầu thủ tục); chỉ có bước thẩm định 20 ngày</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:c1622450-eada-11f0-991f-bbdc27995684#k3:2021-12-05</t>
+          <t>vilextime:T2:provision:ba2dff42-eb6b-11f0-8be9-130a5f277e0a#k4:2017-12-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5893,37 +5881,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Theo quy định về cơ chế một cửa, văn phòng bộ, ngành và Ủy ban nhân dân cấp tỉnh xử lý kết quả đánh giá nội bộ về giải quyết thủ tục hành chính từ phần mềm như thế nào?</t>
+          <t>Một Cảng vụ hàng hải trong quá trình điều tra tai nạn hàng hải thì phải thông báo cho cơ quan điều tra và chuyển giao hồ sơ trong những trường hợp nào?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Điều 30. Đánh giá nội bộ về việc giải quyết thủ tục hành chính</t>
+          <t>Điều 12. Tổ chức điều tra tai nạn hàng hải</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3. Văn phòng bộ, ngành, Ủy ban nhân dân cấp tỉnh có trách nhiệm tổng hợp kết quả đánh giá từ phần mềm để lập báo cáo định kỳ hàng năm lên Văn phòng Chính phủ và công khai kết quả đánh giá nội bộ trên trang thông tin điện tử của bộ, ngành, địa phương.</t>
+          <t>4. Trong quá trình điều tra tai nạn hàng hải, nếu phát hiện có dấu hiệu cấu thành tội phạm thì Giám đốc Cảng vụ hàng hải thông báo cho cơ quan điều tra có thẩm quyền và chuyển giao hồ sơ, tài liệu, vật chứng có liên quan đến vụ tai nạn hàng hải theo yêu cầu của cơ quan điều tra có thẩm quyền; trước khi chuyển giao, hồ sơ, tài liệu phải được sao y hoặc phô tô để lưu lại phục vụ việc điều tra tai nạn hàng hải; việc chuyển giao hồ sơ, tài liệu, vật chứng phải được lập thành biên bản bàn giao.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 30</t>
+          <t>Khoản 4 Điều 12</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>61/2018/NĐ-CP</t>
+          <t>34/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149237</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92556</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5943,11 +5931,12 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:c3251128-2b6a-11f1-9f24-b1fb7d8213f9:2023-01-31</t>
+          <t>vilextime:T2:provision:bdb195ee-df3f-11f0-a46b-f9e80158a78f:2025-06-22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5957,37 +5946,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Trách nhiệm của thuyền phó trong việc lập kế hoạch chuyến đi và giám sát thuyền viên được xác định ra sao?</t>
+          <t>Khi chủ sở hữu đề nghị đóng bãi cất, hạ cánh trên mặt đất mà hồ sơ không hợp lệ, cơ quan nào phải thông báo, bằng hình thức nào và trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Thuyền phó là người giúp việc thuyền trưởng, có trách nhiệm và quyền hạn sau đây:</t>
+          <t>2. Trình tự, thủ tục giải quyết:</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2. Lập kế hoạch chuyến đi, phân công trực ca trình thuyền trưởng duyệt, thường xuyên đôn đốc, hướng dẫn, giám sát thuyền viên thực hiện đúng kế hoạch chuyến đi và nhiệm vụ trực ca.</t>
+          <t>b) Trường hợp hồ sơ không hợp lệ, trong thời hạn 05 ngày làm việc, Bộ Tổng Tham mưu có trách nhiệm thông báo bằng văn bản cho chủ sở hữu bãi cất, hạ cánh để hoàn thiện hồ sơ theo quy định;</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 7</t>
+          <t>Điểm b Khoản 2 Điều 14</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>39/2019/TT-BGTVT</t>
+          <t>42/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138489</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6002,16 +5991,21 @@
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về mở, đóng sân bay chuyên dùng quy định việc xử lý hồ sơ không hợp lệ như thế nào về cơ quan thông báo, hình thức và thời hạn?»; nhãn cũ khong_dat question_ambiguous: Nghị định có cùng điểm b 'hồ sơ không hợp lệ … 05 ngày, Bộ Tổng Tham mưu thông báo' ở Điều 12 (đóng sân bay chuyên dùng), 14, 16 (đóng bãi cất hạ cánh), 17 (đóng tạm thời); câu hỏi không nêu thủ tục nào. Gold là Điều 14 (bãi cất, hạ cánh trên mặt đất)). Câu hỏi chốt đóng bãi cất, hạ cánh trên mặt đất (Điều 14)</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:c4f282ce-28c2-11f1-83e6-3b98479708e7:2025-11-02</t>
+          <t>vilextime:T2:provision:bdb195ee-df3f-11f0-a46b-f9e80158a78f:2025-06-23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6021,37 +6015,37 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Khi tổ chức quản lý, kinh doanh nhà địa phương được giao nhà, đất công kèm máy móc, thiết bị, việc quản lý các tài sản gắn với nhà, đất đó được thực hiện theo quy định nào?</t>
+          <t>Khi chủ sở hữu đề nghị đóng bãi cất, hạ cánh trên mặt đất mà hồ sơ không hợp lệ, cơ quan nào phải thông báo, bằng hình thức nào và trong thời hạn bao lâu?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Điều 1. Phạm vi điều chỉnh</t>
+          <t>2. Trình tự, thủ tục giải quyết:</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3. Đối với tài sản là máy móc, thiết bị và tài sản khác gắn với nhà, đất thuộc phạm vi giao cho tổ chức có chức năng quản lý, kinh doanh nhà địa phương theo quy định tại Điều 5, Điều 6 Nghị định này thì được giao cùng với nhà, đất cho tổ chức có chức năng quản lý, kinh doanh nhà địa phương quản lý, sử dụng và khai thác cùng với nhà, đất được giao; trường hợp không có nhu cầu sử dụng thì thẩm quyền quyết định, trình tự, thủ tục xử lý tài sản được thực hiện như quy định áp dụng đối với đơn vị sự nghiệp công lập quy định tại Luật Quản lý, sử dụng tài sản công, Nghị định của Chính phủ quy định chi tiết thi hành một số điều của Luật Quản lý, sử dụng tài sản công. Việc quản lý, sử dụng số tiền thu được từ xử lý tài sản được thực hiện như quy định về quản lý, sử dụng số tiền thu được từ xử lý tài sản công áp dụng đối với cơ quan nhà nước quy định tại Điều 48 Luật Quản lý, sử dụng tài sản công, Nghị định quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công.</t>
+          <t>b) Trường hợp hồ sơ không hợp lệ, trong thời hạn năm (05) ngày làm việc, kể từ ngày nhận hồ sơ, Cục Tác chiến, Bộ Tổng Tham mưu có văn bản điện tử yêu cầu chủ sở hữu bãi cất, hạ cánh hoàn thiện hồ sơ theo quy định;</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 1</t>
+          <t>Điểm b Khoản 2 Điều 14</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>108/2024/NĐ-CP</t>
+          <t>42/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172735</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141668</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6066,16 +6060,21 @@
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về mở, đóng sân bay chuyên dùng quy định việc xử lý hồ sơ không hợp lệ như thế nào về cơ quan thông báo, hình thức và thời hạn?»; nhãn cũ khong_dat question_ambiguous: Nghị định có cùng điểm b 'hồ sơ không hợp lệ … 05 ngày, Bộ Tổng Tham mưu thông báo' ở Điều 12 (đóng sân bay chuyên dùng), 14, 16 (đóng bãi cất hạ cánh), 17 (đóng tạm thời); câu hỏi không nêu thủ tục nào. Gold là Điều 14 (bãi cất, hạ cánh trên mặt đất)). Câu hỏi chốt đóng bãi cất, hạ cánh trên mặt đất (Điều 14)</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:c72882d4-df55-11f0-a43e-4de24aeeb554#k1:2017-03-14</t>
+          <t>vilextime:T2:provision:c1622450-eada-11f0-991f-bbdc27995684#k3:2021-12-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6085,37 +6084,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Khi hoạt động thanh tra chuyên ngành khoa học và công nghệ giữa các cấp có chồng chéo, Thanh tra Bộ có trách nhiệm gì đối với Tổng cục, Cục và Thanh tra Sở?</t>
+          <t>Theo quy định về cơ chế một cửa, văn phòng bộ, ngành và Ủy ban nhân dân cấp tỉnh xử lý kết quả đánh giá nội bộ về giải quyết thủ tục hành chính từ phần mềm như thế nào?</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2017-03-14</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Điều 12. Mối quan hệ phối hợp trong hoạt động thanh tra ngành Khoa học và Công nghệ</t>
+          <t>Điều 30. Đánh giá nội bộ về việc giải quyết thủ tục hành chính</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1. Thanh tra Bộ hướng dẫn về nghiệp vụ và xử lý chồng chéo trong hoạt động thanh tra chuyên ngành khoa học và công nghệ của Tổng cục, Cục, Thanh tra Cục, Thanh tra Sở.</t>
+          <t>3. Văn phòng bộ, ngành, Ủy ban nhân dân cấp tỉnh có trách nhiệm tổng hợp kết quả đánh giá từ phần mềm để lập báo cáo định kỳ hàng năm lên Văn phòng Chính phủ và công khai kết quả đánh giá nội bộ trên trang thông tin điện tử của bộ, ngành, địa phương.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 12</t>
+          <t>Khoản 3 Điều 30</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>213/2013/NĐ-CP</t>
+          <t>61/2018/NĐ-CP</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32886</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149237</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6135,11 +6134,12 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:c72882d4-df55-11f0-a43e-4de24aeeb554#k1:2017-03-15</t>
+          <t>vilextime:T2:provision:c3251128-2b6a-11f1-9f24-b1fb7d8213f9:2023-01-31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6149,37 +6149,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Khi hoạt động thanh tra chuyên ngành khoa học và công nghệ giữa các cấp có chồng chéo, Thanh tra Bộ có trách nhiệm gì đối với Tổng cục, Cục và Thanh tra Sở?</t>
+          <t>Trách nhiệm của thuyền phó trong việc lập kế hoạch chuyến đi và giám sát thuyền viên được xác định ra sao?</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2017-03-15</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Điều 12. Mối quan hệ phối hợp trong hoạt động thanh tra ngành Khoa học và Công nghệ</t>
+          <t>Thuyền phó là người giúp việc thuyền trưởng, có trách nhiệm và quyền hạn sau đây:</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1. Thanh tra Bộ hướng dẫn về nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ đối với Tổng cục, Cục, Thanh tra Cục, Thanh tra Sở, Chi cục.2. Tổng cục, Cục, Thanh tra Cục thực hiện sự chỉ đạo về công tác, hướng dẫn về nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ của Thanh tra Bộ; hỗ trợ Thanh tra Bộ hướng dẫn nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ đối với Thanh tra Sở, Chi cục; phối hợp với Thanh tra Sở, Chi cục khi tiến hành hoạt động thanh tra chuyên ngành thuộc thẩm quyền được giao.</t>
+          <t>2. Lập kế hoạch chuyến đi, phân công trực ca trình thuyền trưởng duyệt, thường xuyên đôn đốc, hướng dẫn, giám sát thuyền viên thực hiện đúng kế hoạch chuyến đi và nhiệm vụ trực ca.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 12</t>
+          <t>Khoản 2 Điều 7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>213/2013/NĐ-CP</t>
+          <t>39/2019/TT-BGTVT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32886</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138489</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6193,25 +6193,18 @@
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Phiên bản 2 bỏ 'xử lý chồng chéo' (đáp án đúng ở mốc này: Thanh tra Bộ chỉ hướng dẫn nghiệp vụ). Văn bản đáp án dính cả khoản 2 ('…Chi cục.2. Tổng cục, Cục…')</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:cb760cda-2de8-11f1-bb20-c1882ef56e4a:2022-05-31</t>
+          <t>vilextime:T2:provision:c4f282ce-28c2-11f1-83e6-3b98479708e7:2025-11-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6221,37 +6214,37 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thẩm quyền quyết định chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài được xác định ra sao?</t>
+          <t>Khi tổ chức quản lý, kinh doanh nhà địa phương được giao nhà, đất công kèm máy móc, thiết bị, việc quản lý các tài sản gắn với nhà, đất đó được thực hiện theo quy định nào?</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Điều 17. Chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài</t>
+          <t>Điều 1. Phạm vi điều chỉnh</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3. Thẩm quyền quyết định chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài: Người có thẩm quyền cho phép thành lập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài theo quy định tại Điều 13 Nghị định này có quyền quyết định cho phép chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài.</t>
+          <t>3. Đối với tài sản là máy móc, thiết bị và tài sản khác gắn với nhà, đất thuộc phạm vi giao cho tổ chức có chức năng quản lý, kinh doanh nhà địa phương theo quy định tại Điều 5, Điều 6 Nghị định này thì được giao cùng với nhà, đất cho tổ chức có chức năng quản lý, kinh doanh nhà địa phương quản lý, sử dụng và khai thác cùng với nhà, đất được giao; trường hợp không có nhu cầu sử dụng thì thẩm quyền quyết định, trình tự, thủ tục xử lý tài sản được thực hiện như quy định áp dụng đối với đơn vị sự nghiệp công lập quy định tại Luật Quản lý, sử dụng tài sản công, Nghị định của Chính phủ quy định chi tiết thi hành một số điều của Luật Quản lý, sử dụng tài sản công. Việc quản lý, sử dụng số tiền thu được từ xử lý tài sản được thực hiện như quy định về quản lý, sử dụng số tiền thu được từ xử lý tài sản công áp dụng đối với cơ quan nhà nước quy định tại Điều 48 Luật Quản lý, sử dụng tài sản công, Nghị định quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 17</t>
+          <t>Khoản 3 Điều 1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>15/2019/NĐ-CP</t>
+          <t>108/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134195</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172735</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6271,11 +6264,12 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:cf4ee8a0-1e2e-11f1-bb92-f7181c000d19:2021-08-15</t>
+          <t>vilextime:T2:provision:c72882d4-df55-11f0-a43e-4de24aeeb554#k1:2017-03-14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6285,37 +6279,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Khi thành lập Hội đồng xử lý rủi ro của Ngân hàng Nhà nước, thành viên giữ vị trí Phó Chủ tịch thường trực được xác định như thế nào?</t>
+          <t>Khi hoạt động thanh tra chuyên ngành khoa học và công nghệ giữa các cấp có chồng chéo, Thanh tra Bộ có trách nhiệm gì đối với Tổng cục, Cục và Thanh tra Sở?</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2017-03-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2. Các thành viên Hội đồng:</t>
+          <t>Điều 12. Mối quan hệ phối hợp trong hoạt động thanh tra ngành Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>a) Vụ trưởng Vụ Tài chính - Kế toán, Phó Chủ tịch thường trực;</t>
+          <t>1. Thanh tra Bộ hướng dẫn về nghiệp vụ và xử lý chồng chéo trong hoạt động thanh tra chuyên ngành khoa học và công nghệ của Tổng cục, Cục, Thanh tra Cục, Thanh tra Sở.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 12</t>
+          <t>Khoản 1 Điều 12</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>39/2013/TT-NHNN</t>
+          <t>213/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=42495</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32886</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6330,20 +6324,17 @@
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Phiên bản 2: chức danh (Vụ trưởng hoặc Phó Vụ trưởng) nằm ở câu dẫn</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:cf4ee8a0-1e2e-11f1-bb92-f7181c000d19:2021-08-16</t>
+          <t>vilextime:T2:provision:c72882d4-df55-11f0-a43e-4de24aeeb554#k1:2017-03-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6353,37 +6344,37 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Khi thành lập Hội đồng xử lý rủi ro của Ngân hàng Nhà nước, thành viên giữ vị trí Phó Chủ tịch thường trực được xác định như thế nào?</t>
+          <t>Khi hoạt động thanh tra chuyên ngành khoa học và công nghệ giữa các cấp có chồng chéo, Thanh tra Bộ có trách nhiệm gì đối với Tổng cục, Cục và Thanh tra Sở?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2017-03-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2. Các thành viên Hội đồng bao gồm Chánh Thanh tra, giám sát ngân hàng hoặc Phó Chánh Thanh tra, giám sát ngân hàng, Vụ trưởng hoặc Phó Vụ trưởng, Cục trưởng hoặc Phó Cục trưởng các đơn vị Ngân hàng Nhà nước sau:</t>
+          <t>Điều 12. Mối quan hệ phối hợp trong hoạt động thanh tra ngành Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>a) Vụ Tài chính - Kế toán: Phó Chủ tịch thường trực;</t>
+          <t>1. Thanh tra Bộ hướng dẫn về nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ đối với Tổng cục, Cục, Thanh tra Cục, Thanh tra Sở, Chi cục.2. Tổng cục, Cục, Thanh tra Cục thực hiện sự chỉ đạo về công tác, hướng dẫn về nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ của Thanh tra Bộ; hỗ trợ Thanh tra Bộ hướng dẫn nghiệp vụ thanh tra chuyên ngành khoa học và công nghệ đối với Thanh tra Sở, Chi cục; phối hợp với Thanh tra Sở, Chi cục khi tiến hành hoạt động thanh tra chuyên ngành thuộc thẩm quyền được giao.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 12</t>
+          <t>Khoản 1 Điều 12</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>39/2013/TT-NHNN</t>
+          <t>213/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=42495</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32886</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6397,21 +6388,26 @@
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Phiên bản 2: chức danh (Vụ trưởng hoặc Phó Vụ trưởng) nằm ở câu dẫn</t>
+          <t>Phiên bản 2 bỏ 'xử lý chồng chéo' (đáp án đúng ở mốc này: Thanh tra Bộ chỉ hướng dẫn nghiệp vụ). Văn bản đáp án dính cả khoản 2 ('…Chi cục.2. Tổng cục, Cục…')</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:d3fb9d0a-eb78-11f0-b651-0345ace237f1:2025-08-14</t>
+          <t>vilextime:T2:provision:cb760cda-2de8-11f1-bb20-c1882ef56e4a:2022-05-31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6421,37 +6417,37 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pháp luật về đất đai quy định việc xử lý giá trị tài sản còn lại của người có đất bị thu hồi do vi phạm như thế nào?</t>
+          <t>Thẩm quyền quyết định chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài được xác định ra sao?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>7. Xử lý tài sản trên đất, giá trị tài sản còn lại của người có đất thu hồi</t>
+          <t>Điều 17. Chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>a) Trường hợp thu hồi đất theo quy định tại khoản 6 Điều 81 Luật Đất đai thì số tiền sử dụng đất thu được từ bán đấu giá quyền sử dụng đất, tài sản gắn liền với đất (nếu có) sau khi trừ đi các chi phí cưỡng chế, tổ chức đấu giá theo quy định được nộp ngân sách nhà nước để thanh toán nghĩa vụ tài chính của người sử dụng đất, số tiền còn lại được hoàn trả cho người có đất thu hồi, chủ sở hữu tài sản gắn liền với đất thu hồi;</t>
+          <t>3. Thẩm quyền quyết định chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài: Người có thẩm quyền cho phép thành lập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài theo quy định tại Điều 13 Nghị định này có quyền quyết định cho phép chia, tách, sáp nhập cơ sở giáo dục nghề nghiệp có vốn đầu tư nước ngoài.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 7 Điều 32</t>
+          <t>Khoản 3 Điều 17</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>102/2024/NĐ-CP</t>
+          <t>15/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134195</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6461,33 +6457,22 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>'Thu hồi do vi phạm' gồm nhiều trường hợp của Điều 81 Luật Đất đai; điểm b (khoản 7 Điều 81) cũng quy định xử lý giá trị tài sản còn lại</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>b) Trường hợp thu hồi đất theo quy định tại khoản 7 Điều 81 Luật Đất đai thì trong thời hạn 12 tháng...</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:d3fb9d0a-eb78-11f0-b651-0345ace237f1:2025-08-15</t>
+          <t>vilextime:T2:provision:cf4ee8a0-1e2e-11f1-bb92-f7181c000d19:2021-08-15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6497,37 +6482,37 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pháp luật về đất đai quy định việc xử lý giá trị tài sản còn lại của người có đất bị thu hồi do vi phạm như thế nào?</t>
+          <t>Khi thành lập Hội đồng xử lý rủi ro của Ngân hàng Nhà nước, thành viên giữ vị trí Phó Chủ tịch thường trực được xác định như thế nào?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>7. Xử lý tài sản trên đất, giá trị tài sản còn lại của người có đất thu hồi</t>
+          <t>2. Các thành viên Hội đồng:</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>a) Trường hợp thu hồi đất theo quy định tại khoản 6 Điều 81 Luật Đất đai thì giá trị tài sản được xác định tại thời điểm quyết định thu hồi đất do Hội đồng định giá tài sản xác định. Trong thời hạn 10 ngày kể từ ngày có quyết định thu hồi đất, cơ quan có chức năng quản lý đất đai trình cấp có thẩm quyền thu hồi đất thành lập Hội đồng định giá tài sản. Giá trị tài sản còn lại sau khi trừ đi các chi phí để thu hồi đất, bao gồm chi phí lập hồ sơ thu hồi đất, chi phí cưỡng chế thu hồi đất (nếu có), chi phí định giá tài sản và các chi phí khác để thu hồi đất, được hoàn trả cho chủ sở hữu tài sản gắn liền với đất thu hồi trong thời hạn không quá 30 ngày kể từ ngày nhà đầu tư khác được Nhà nước giao đất, cho thuê đất nộp nghĩa vụ tài chính bằng hoặc lớn hơn số tiền hoàn trả nêu trên.</t>
+          <t>a) Vụ trưởng Vụ Tài chính - Kế toán, Phó Chủ tịch thường trực;</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 7 Điều 32</t>
+          <t>Điểm a Khoản 2 Điều 12</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>102/2024/NĐ-CP</t>
+          <t>39/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=42495</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6537,33 +6522,26 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>'Thu hồi do vi phạm' gồm nhiều trường hợp của Điều 81 Luật Đất đai; điểm b (khoản 7 Điều 81) cũng quy định xử lý giá trị tài sản còn lại</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>b) Trường hợp thu hồi đất theo quy định tại khoản 7 Điều 81 Luật Đất đai thì trong thời hạn 12 tháng...</t>
-        </is>
-      </c>
+          <t>Phiên bản 2: chức danh (Vụ trưởng hoặc Phó Vụ trưởng) nằm ở câu dẫn</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:d4dcee26-df49-11f0-ab3e-ffb50be130e6#k1#d:2016-02-15</t>
+          <t>vilextime:T2:provision:cf4ee8a0-1e2e-11f1-bb92-f7181c000d19:2021-08-16</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6573,37 +6551,37 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Trường hợp một doanh nghiệp đề nghị cấp giấy phép vận chuyển hàng nguy hiểm bằng xe cơ giới đường bộ, giấy chứng nhận của người lái xe và người áp tải phải nộp dưới hình thức bản nào?</t>
+          <t>Khi thành lập Hội đồng xử lý rủi ro của Ngân hàng Nhà nước, thành viên giữ vị trí Phó Chủ tịch thường trực được xác định như thế nào?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2016-02-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1. Hồ sơ đề nghị cấp Giấy phép vận chuyển hàng nguy hiểm bằng phương tiện giao thông cơ giới đường bộ bao gồm:</t>
+          <t>2. Các thành viên Hội đồng bao gồm Chánh Thanh tra, giám sát ngân hàng hoặc Phó Chánh Thanh tra, giám sát ngân hàng, Vụ trưởng hoặc Phó Vụ trưởng, Cục trưởng hoặc Phó Cục trưởng các đơn vị Ngân hàng Nhà nước sau:</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>d) Bản sao từ sổ gốc hoặc bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu (trường hợp cá nhân, tổ chức nộp hồ sơ trực tiếp) Giấy chứng nhận cần thiết còn hiệu lực của người điều khiển phương tiện vận chuyển và người áp tải hàng nguy hiểm theo quy định tại Khoản 2 Điều 10 Thông tư này;</t>
+          <t>a) Vụ Tài chính - Kế toán: Phó Chủ tịch thường trực;</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1 Điều 13</t>
+          <t>Điểm a Khoản 2 Điều 12</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>52/2013/TT-BTNMT</t>
+          <t>39/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=41425</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=42495</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6618,16 +6596,21 @@
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Phiên bản 2: chức danh (Vụ trưởng hoặc Phó Vụ trưởng) nằm ở câu dẫn</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:d8217e92-eb80-11f0-8e19-7bcbed515534#k8#c:2017-05-19</t>
+          <t>vilextime:T2:provision:d3fb9d0a-eb78-11f0-b651-0345ace237f1:2025-08-14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6637,37 +6620,37 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Một người có tang vật là động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?</t>
+          <t>Khi đất bị thu hồi vì người sử dụng đất không thực hiện nghĩa vụ tài chính với Nhà nước, giá trị tài sản còn lại trên đất được xác định và xử lý như thế nào?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2017-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>8. Phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng đối với hành vi có tang vật vi phạm thuộc một trong các trường hợp sau:</t>
+          <t>7. Xử lý tài sản trên đất, giá trị tài sản còn lại của người có đất thu hồi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>c) Động vật rừng hoặc bộ phận, dẫn xuất của chúng thuộc loài nguy cấp, quý, hiếm nhóm IB có giá trị từ trên 80.000.000 đồng đến 100.000.000 đồng.</t>
+          <t>a) Trường hợp thu hồi đất theo quy định tại khoản 6 Điều 81 Luật Đất đai thì số tiền sử dụng đất thu được từ bán đấu giá quyền sử dụng đất, tài sản gắn liền với đất (nếu có) sau khi trừ đi các chi phí cưỡng chế, tổ chức đấu giá theo quy định được nộp ngân sách nhà nước để thanh toán nghĩa vụ tài chính của người sử dụng đất, số tiền còn lại được hoàn trả cho người có đất thu hồi, chủ sở hữu tài sản gắn liền với đất thu hồi;</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 8 Điều 21</t>
+          <t>Điểm a Khoản 7 Điều 32</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>157/2013/NĐ-CP</t>
+          <t>102/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32584</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6677,33 +6660,26 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Cùng khoản 8, điểm d (nuôi trái phép từ 07 đến 08 cá thể động vật rừng nhóm IB) cũng là trường hợp có tang vật nhóm IB bị phạt 300–400 triệu</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>d) Nuôi trái phép từ 07 đến 08 cá thể động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB.</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về đất đai quy định việc xử lý giá trị tài sản còn lại của người có đất bị thu hồi do vi phạm như thế nào?»; nhãn cũ khong_dat question_ambiguous: 'Thu hồi do vi phạm' gồm nhiều trường hợp của Điều 81 Luật Đất đai; điểm b (khoản 7 Điều 81) cũng quy định xử lý giá trị tài sản còn lại). Câu hỏi chốt thu hồi do không thực hiện nghĩa vụ tài chính (khoản 6 Điều 81 Luật Đất đai), chỉ khớp điểm a</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:d8217e92-eb80-11f0-8e19-7bcbed515534#k8#c:2017-05-20</t>
+          <t>vilextime:T2:provision:d3fb9d0a-eb78-11f0-b651-0345ace237f1:2025-08-15</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6713,37 +6689,37 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Một người có tang vật là động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?</t>
+          <t>Khi đất bị thu hồi vì người sử dụng đất không thực hiện nghĩa vụ tài chính với Nhà nước, giá trị tài sản còn lại trên đất được xác định và xử lý như thế nào?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2017-05-20</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>8. Phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng đối với hành vi có tang vật vi phạm thuộc một trong các trường hợp sau:</t>
+          <t>7. Xử lý tài sản trên đất, giá trị tài sản còn lại của người có đất thu hồi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>c) Động vật rừng hoặc bộ phận từ 07 đến 08 cá thể thuộc loài nguy cấp, quý, hiếm nhóm IB.</t>
+          <t>a) Trường hợp thu hồi đất theo quy định tại khoản 6 Điều 81 Luật Đất đai thì giá trị tài sản được xác định tại thời điểm quyết định thu hồi đất do Hội đồng định giá tài sản xác định. Trong thời hạn 10 ngày kể từ ngày có quyết định thu hồi đất, cơ quan có chức năng quản lý đất đai trình cấp có thẩm quyền thu hồi đất thành lập Hội đồng định giá tài sản. Giá trị tài sản còn lại sau khi trừ đi các chi phí để thu hồi đất, bao gồm chi phí lập hồ sơ thu hồi đất, chi phí cưỡng chế thu hồi đất (nếu có), chi phí định giá tài sản và các chi phí khác để thu hồi đất, được hoàn trả cho chủ sở hữu tài sản gắn liền với đất thu hồi trong thời hạn không quá 30 ngày kể từ ngày nhà đầu tư khác được Nhà nước giao đất, cho thuê đất nộp nghĩa vụ tài chính bằng hoặc lớn hơn số tiền hoàn trả nêu trên.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 8 Điều 21</t>
+          <t>Điểm a Khoản 7 Điều 32</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>157/2013/NĐ-CP</t>
+          <t>102/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32584</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169363</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6753,33 +6729,26 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Cùng khoản 8, điểm d (nuôi trái phép từ 07 đến 08 cá thể động vật rừng nhóm IB) cũng là trường hợp có tang vật nhóm IB bị phạt 300–400 triệu</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>d) Nuôi trái phép từ 07 đến 08 cá thể động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB.</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về đất đai quy định việc xử lý giá trị tài sản còn lại của người có đất bị thu hồi do vi phạm như thế nào?»; nhãn cũ khong_dat question_ambiguous: 'Thu hồi do vi phạm' gồm nhiều trường hợp của Điều 81 Luật Đất đai; điểm b (khoản 7 Điều 81) cũng quy định xử lý giá trị tài sản còn lại). Câu hỏi chốt thu hồi do không thực hiện nghĩa vụ tài chính (khoản 6 Điều 81 Luật Đất đai), chỉ khớp điểm a</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:dd3dceec-eb7d-11f0-a907-eddde982ba1f#k2:2024-01-31</t>
+          <t>vilextime:T2:provision:d4dcee26-df49-11f0-ab3e-ffb50be130e6#k1#d:2016-02-15</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6789,37 +6758,37 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pháp luật về tải trọng, khổ giới hạn đường bộ quy định khổ giới hạn về chiều cao của đường bộ như thế nào?</t>
+          <t>Trường hợp một doanh nghiệp đề nghị cấp giấy phép vận chuyển hàng nguy hiểm bằng xe cơ giới đường bộ, giấy chứng nhận của người lái xe và người áp tải phải nộp dưới hình thức bản nào?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2016-02-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Điều 5. Khổ giới hạn của đường bộ</t>
+          <t>1. Hồ sơ đề nghị cấp Giấy phép vận chuyển hàng nguy hiểm bằng phương tiện giao thông cơ giới đường bộ bao gồm:</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2. Khổ giới hạn về chiều cao của đường bộ là 4,75 mét đối với đường cao tốc, đường cấp I, II, III và 4,5 mét đối với đường cấp IV trở xuống.</t>
+          <t>d) Bản sao từ sổ gốc hoặc bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu (trường hợp cá nhân, tổ chức nộp hồ sơ trực tiếp) Giấy chứng nhận cần thiết còn hiệu lực của người điều khiển phương tiện vận chuyển và người áp tải hàng nguy hiểm theo quy định tại Khoản 2 Điều 10 Thông tư này;</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 5</t>
+          <t>Điểm d Khoản 1 Điều 13</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>46/2015/TT-BGTVT</t>
+          <t>52/2013/TT-BTNMT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=85825</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=41425</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6839,11 +6808,12 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:dd3dceec-eb7d-11f0-a907-eddde982ba1f#k2:2024-02-01</t>
+          <t>vilextime:T2:provision:d8217e92-eb80-11f0-8e19-7bcbed515534#k8#c:2017-05-19</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6853,37 +6823,37 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pháp luật về tải trọng, khổ giới hạn đường bộ quy định khổ giới hạn về chiều cao của đường bộ như thế nào?</t>
+          <t>Một người có tang vật là động vật rừng hoặc bộ phận của động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB, không phải trường hợp nuôi trái phép, thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2017-05-19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Điều 5. Khổ giới hạn của đường bộ</t>
+          <t>8. Phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng đối với hành vi có tang vật vi phạm thuộc một trong các trường hợp sau:</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2. Khổ giới hạn về chiều cao của đường bộ là 4,75 mét đối với đường cao tốc, đường cấp I, II, III và 4,5 mét đối với đường cấp IV trở xuống hoặc được thể hiện bằng biển báo hiệu “Hạn chế chiều cao” theo quy định về báo hiệu đường bộ.</t>
+          <t>c) Động vật rừng hoặc bộ phận, dẫn xuất của chúng thuộc loài nguy cấp, quý, hiếm nhóm IB có giá trị từ trên 80.000.000 đồng đến 100.000.000 đồng.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 5</t>
+          <t>Điểm c Khoản 8 Điều 21</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>46/2015/TT-BGTVT</t>
+          <t>157/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=85825</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32584</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6898,16 +6868,21 @@
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người có tang vật là động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?»; nhãn cũ khong_dat question_ambiguous: Cùng khoản 8, điểm d (nuôi trái phép từ 07 đến 08 cá thể động vật rừng nhóm IB) cũng là trường hợp có tang vật nhóm IB bị phạt 300–400 triệu). Câu hỏi loại trường hợp nuôi trái phép (điểm d)</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:dea1606a-2d44-11f1-a4ba-79faf33b0cc5:2025-11-17</t>
+          <t>vilextime:T2:provision:d8217e92-eb80-11f0-8e19-7bcbed515534#k8#c:2017-05-20</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6917,37 +6892,37 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Một Tổng cục trưởng Tổng cục Quản lý thị trường xử phạt vi phạm trong lĩnh vực thủy sản thì được áp dụng những biện pháp khắc phục hậu quả nào?</t>
+          <t>Một người có tang vật là động vật rừng hoặc bộ phận của động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB, không phải trường hợp nuôi trái phép, thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4. Cục trưởng Cục Quản lý và Phát triển thị trường trong nước có quyền:</t>
+          <t>8. Phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng đối với hành vi có tang vật vi phạm thuộc một trong các trường hợp sau:</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và các biện pháp khắc phục hậu quả tương ứng quy định tại khoản 3 Điều 4 Nghị định này.</t>
+          <t>c) Động vật rừng hoặc bộ phận từ 07 đến 08 cá thể thuộc loài nguy cấp, quý, hiếm nhóm IB.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 4 Điều 51</t>
+          <t>Điểm c Khoản 8 Điều 21</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>38/2024/NĐ-CP</t>
+          <t>157/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166564</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32584</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6957,29 +6932,26 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>unanswerable_as_asked</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Ở phiên bản 2 không còn chức danh Tổng cục trưởng Tổng cục Quản lý thị trường; khoản 4 nay trao quyền cho Cục trưởng Cục Quản lý và Phát triển thị trường trong nước. Đề xuất sửa câu hỏi thành 'người đứng đầu cơ quan quản lý thị trường ở trung ương'</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một người có tang vật là động vật rừng thuộc loài nguy cấp, quý, hiếm nhóm IB thì trong trường hợp nào bị áp dụng mức phạt tiền từ 300.000.000 đồng đến 400.000.000 đồng?»; nhãn cũ khong_dat question_ambiguous: Cùng khoản 8, điểm d (nuôi trái phép từ 07 đến 08 cá thể động vật rừng nhóm IB) cũng là trường hợp có tang vật nhóm IB bị phạt 300–400 triệu). Câu hỏi loại trường hợp nuôi trái phép (điểm d)</t>
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e23c54c0-3634-11f1-9175-9b33751e108f:2011-09-07</t>
+          <t>vilextime:T2:provision:dd3dceec-eb7d-11f0-a907-eddde982ba1f#k2:2024-01-31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6989,37 +6961,37 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực đưa người vào cơ sở chữa bệnh, việc giảm thời hạn, tạm đình chỉ hoặc miễn chấp hành quyết định được xem xét và quyết định theo trình tự nào?</t>
+          <t>Pháp luật về tải trọng, khổ giới hạn đường bộ quy định khổ giới hạn về chiều cao của đường bộ như thế nào?</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2011-09-07</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hàng tháng, Ban Giám đốc Trung tâm Chữa bệnh - Giáo dục - Lao động xã hội nhận xét, đánh giá kết quả lao động, học tập và chữa bệnh của người bị áp dụng biện pháp đưa vào cơ sở chữa bệnh để theo dõi quá trình rèn luyện, tu dưỡng và chữa trị.</t>
+          <t>Điều 5. Khổ giới hạn của đường bộ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3. Chủ tịch Uỷ ban nhân dân cấp huyện nơi đã ra quyết định đưa vào cơ sở chữa bệnh quyết định việc giảm thời hạn, tạm đình chỉ hoặc miễn việc chấp hành quy định tại khoản 1 và khoản 2 Điều này trên cơ sở đề nghị của Giám đốc Trung tâm Chữa bệnh - Giáo dục - Lao động xã hội.</t>
+          <t>2. Khổ giới hạn về chiều cao của đường bộ là 4,75 mét đối với đường cao tốc, đường cấp I, II, III và 4,5 mét đối với đường cấp IV trở xuống.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 61</t>
+          <t>Khoản 2 Điều 5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>135/2004/NĐ-CP</t>
+          <t>46/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19676</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=85825</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -7033,25 +7005,18 @@
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lead_in_wrong</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>Câu dẫn phiên bản 1 là đoạn 'Hàng tháng, Ban Giám đốc Trung tâm… nhận xét, đánh giá…', không phải tiêu đề Điều 61 như phiên bản 2</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e2acf6a0-eae2-11f0-bd05-d766c03bb281#k4:2022-03-15</t>
+          <t>vilextime:T2:provision:dd3dceec-eb7d-11f0-a907-eddde982ba1f#k2:2024-02-01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7061,37 +7026,37 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nếu một ngân hàng thương mại tự nguyện chấm dứt hoạt động chi nhánh hoặc phòng giao dịch, thì văn bản chấp thuận của cơ quan nào là mốc tính thời hạn thực hiện?</t>
+          <t>Pháp luật về tải trọng, khổ giới hạn đường bộ quy định khổ giới hạn về chiều cao của đường bộ như thế nào?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Điều 24. Tự nguyện chấm dứt hoạt động chi nhánh, phòng giao dịch, văn phòng đại diện, đơn vị sự nghiệp ở trong nước</t>
+          <t>Điều 5. Khổ giới hạn của đường bộ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4. Trong thời hạn 45 ngày kể từ ngày có văn bản chấp thuận của Ngân hàng Nhà nước chi nhánh nơi đặt trụ sở chi nhánh, phòng giao dịch quy định tại điểm b khoản 2 và điểm b khoản 3 Điều này, ngân hàng thương mại phải tiến hành các thủ tục pháp lý theo quy định của pháp luật để chấm dứt hoạt động của chi nhánh, phòng giao dịch; có văn bản báo cáo Ngân hàng Nhà nước (qua Cơ quan Thanh tra, giám sát ngân hàng) và Ngân hàng Nhà nước chi nhánh nơi đặt trụ sở chi nhánh, phòng giao dịch về ngày chấm dứt hoạt động.</t>
+          <t>2. Khổ giới hạn về chiều cao của đường bộ là 4,75 mét đối với đường cao tốc, đường cấp I, II, III và 4,5 mét đối với đường cấp IV trở xuống hoặc được thể hiện bằng biển báo hiệu “Hạn chế chiều cao” theo quy định về báo hiệu đường bộ.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 24</t>
+          <t>Khoản 2 Điều 5</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>21/2013/TT-NHNN</t>
+          <t>46/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43235</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=85825</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7111,11 +7076,12 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e653e450-2ab9-11f1-8795-75a5ce3bd467:2025-03-01</t>
+          <t>vilextime:T2:provision:dea1606a-2d44-11f1-a4ba-79faf33b0cc5:2025-11-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7125,37 +7091,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Theo quy định về điều tra tai nạn giao thông đường sắt, Cảnh sát giao thông được tạm giữ những gì liên quan đến phương tiện và người điều khiển phương tiện đường bộ?</t>
+          <t>Người đứng đầu cơ quan quản lý thị trường ở trung ương xử phạt vi phạm hành chính trong lĩnh vực thủy sản thì được áp dụng những biện pháp khắc phục hậu quả nào?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Điều 15. Một số hoạt động thu thập tài liệu khác liên quan đến vụ tai nạn</t>
+          <t>4. Tổng cục trưởng Tổng cục Quản lý thị trường có quyền:</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1. Tạm giữ tang vật, phương tiện, giấy phép, chứng chỉ hành nghề của người điều khiển phương tiện đường bộ liên quan đến vụ tai nạn giao thông đường sắt được thực hiện theo quy định tại Điều 125 Luật Xử lý vi phạm hành chính năm 2012 (sửa đổi, bổ sung năm 2020) và các quy định khác có liên quan. Đối với trường hợp các giấy tờ có liên quan đến người và phương tiện giao thông đã được tích hợp trong căn cước điện tử, tài khoản định danh điện tử trên Ứng dụng định danh quốc gia, khi tạm giữ giấy tờ, Cảnh sát giao thông thực hiện việc tạm giữ giấy tờ trên môi trường điện tử. Việc xử lý tang vật, phương tiện, giấy phép, chứng chỉ hành nghề của người điều khiển phương tiện liên quan đến vụ tai nạn giao thông đường sắt được thực hiện theo quy định tại Điều 126 Luật Xử lý vi phạm hành chính năm 2012 (sửa đổi, bổ sung năm 2020) và các quy định khác có liên quan.</t>
+          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại các điểm a, d, đ, e và g khoản 1 Điều 28 Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 Nghị định này.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 15</t>
+          <t>Điểm d Khoản 4 Điều 51</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>34/2018/TT-BCA</t>
+          <t>38/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177104</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166564</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -7170,16 +7136,21 @@
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một Tổng cục trưởng Tổng cục Quản lý thị trường xử phạt vi phạm trong lĩnh vực thủy sản thì được áp dụng những biện pháp khắc phục hậu quả nào?»; nhãn cũ dat: ). Câu hỏi gọi chức danh theo vai (người đứng đầu cơ quan quản lý thị trường ở trung ương), đúng cho cả hai phiên bản</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e902d34e-df52-11f0-b1c8-1baca6cbd210:2021-12-31</t>
+          <t>vilextime:T2:provision:dea1606a-2d44-11f1-a4ba-79faf33b0cc5:2025-11-17</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7189,37 +7160,37 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thẩm quyền tịch thu tang vật, phương tiện vi phạm hành chính trong lĩnh vực giáo dục của Chủ tịch Ủy ban nhân dân cấp huyện bị giới hạn như thế nào về giá trị?</t>
+          <t>Người đứng đầu cơ quan quản lý thị trường ở trung ương xử phạt vi phạm hành chính trong lĩnh vực thủy sản thì được áp dụng những biện pháp khắc phục hậu quả nào?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2. Chủ tịch Ủy ban nhân dân huyện, quận, thị xã, thành phố trực thuộc tỉnh (cấp huyện) có quyền:</t>
+          <t>4. Cục trưởng Cục Quản lý và Phát triển thị trường trong nước có quyền:</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt quy định tại điểm b khoản này;</t>
+          <t>d) Áp dụng biện pháp khắc phục hậu quả quy định tại khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và các biện pháp khắc phục hậu quả tương ứng quy định tại khoản 3 Điều 4 Nghị định này.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 36</t>
+          <t>Điểm d Khoản 4 Điều 51</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>04/2021/NĐ-CP</t>
+          <t>38/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148174</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166564</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7234,16 +7205,21 @@
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một Tổng cục trưởng Tổng cục Quản lý thị trường xử phạt vi phạm trong lĩnh vực thủy sản thì được áp dụng những biện pháp khắc phục hậu quả nào?»; nhãn cũ khong_dat unanswerable_as_asked: Ở phiên bản 2 không còn chức danh Tổng cục trưởng Tổng cục Quản lý thị trường; khoản 4 nay trao quyền cho Cục trưởng Cục Quản lý và Phát triển thị trường trong nước. Đề xuất sửa câu hỏi thành 'người đứng đầu cơ quan quản lý thị trường ở trung ương'). Câu hỏi gọi chức danh theo vai (người đứng đầu cơ quan quản lý thị trường ở trung ương), đúng cho cả hai phiên bản</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e93ccd50-2c83-11f1-bc09-954fa6134772:2023-07-18</t>
+          <t>vilextime:T2:provision:e23c54c0-3634-11f1-9175-9b33751e108f:2011-09-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7253,37 +7229,37 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Trường hợp đăng ký một quy chuẩn kỹ thuật đã ban hành, hồ sơ và thủ tục đăng ký được thực hiện theo quy định nào?</t>
+          <t>Trong lĩnh vực đưa người vào cơ sở chữa bệnh, việc giảm thời hạn, tạm đình chỉ hoặc miễn chấp hành quyết định được xem xét và quyết định theo trình tự nào?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2011-09-07</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Điều 14. Thông báo, phổ biến, đăng ký, xuất bản, phát hành quy chuẩn kỹ thuật</t>
+          <t>Hàng tháng, Ban Giám đốc Trung tâm Chữa bệnh - Giáo dục - Lao động xã hội nhận xét, đánh giá kết quả lao động, học tập và chữa bệnh của người bị áp dụng biện pháp đưa vào cơ sở chữa bệnh để theo dõi quá trình rèn luyện, tu dưỡng và chữa trị.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4. Hồ sơ, thủ tục đăng ký quy chuẩn kỹ thuật đã ban hành thực hiện theo quy định tại Điều 13 Nghị định số 127/2007/NĐ-CP. Bản đăng ký quy chuẩn kỹ thuật được lập theo Mẫu quy định tại Phụ lục XI kèm theo Thông tư này.</t>
+          <t>3. Chủ tịch Uỷ ban nhân dân cấp huyện nơi đã ra quyết định đưa vào cơ sở chữa bệnh quyết định việc giảm thời hạn, tạm đình chỉ hoặc miễn việc chấp hành quy định tại khoản 1 và khoản 2 Điều này trên cơ sở đề nghị của Giám đốc Trung tâm Chữa bệnh - Giáo dục - Lao động xã hội.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 14</t>
+          <t>Khoản 3 Điều 61</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>26/2019/TT-BKHCN</t>
+          <t>135/2004/NĐ-CP</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146540</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=19676</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7297,21 +7273,26 @@
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>lead_in_wrong</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Chỗ đổi chính là thêm Mẫu bản đăng ký (Phụ lục XI); căn cứ Điều 13 NĐ 127/2007 giữ nguyên</t>
+          <t>Câu dẫn phiên bản 1 là đoạn 'Hàng tháng, Ban Giám đốc Trung tâm… nhận xét, đánh giá…', không phải tiêu đề Điều 61 như phiên bản 2</t>
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:e9b9d5f4-df42-11f0-a5f2-138bc0b82b6b:2025-07-01</t>
+          <t>vilextime:T2:provision:e2acf6a0-eae2-11f0-bd05-d766c03bb281#k4:2022-03-15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7321,37 +7302,37 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nếu một địa phương được chọn đặt địa điểm thi hành án tử hình bằng tiêm thuốc độc, thì Ủy ban nhân dân cấp tỉnh có trách nhiệm gì và chỉ đạo chính quyền cấp nào phối hợp?</t>
+          <t>Nếu một ngân hàng thương mại tự nguyện chấm dứt hoạt động chi nhánh hoặc phòng giao dịch, thì văn bản chấp thuận của cơ quan nào là mốc tính thời hạn thực hiện?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mục 3 TRÁCH NHIỆM CỦA CÁC BỘ VÀ ỦY BAN NHÂN DÂN CÁC CẤP TRONG THI HÀNH ÁN TỬ HÌNH</t>
+          <t>Điều 24. Tự nguyện chấm dứt hoạt động chi nhánh, phòng giao dịch, văn phòng đại diện, đơn vị sự nghiệp ở trong nước</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Điều 20. Trách nhiệm của Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương có trách nhiệm cấp đất để xây dựng địa điểm thi hành án tử hình, chỉ định nơi mai táng người bị thi hành án tử hình; chỉ đạo Ủy ban nhân dân cấp xã, các cơ quan liên quan ở địa phương phối hợp bảo đảm an ninh, trật tự, an toàn cho việc thi hành án tử hình.</t>
+          <t>4. Trong thời hạn 45 ngày kể từ ngày có văn bản chấp thuận của Ngân hàng Nhà nước chi nhánh nơi đặt trụ sở chi nhánh, phòng giao dịch quy định tại điểm b khoản 2 và điểm b khoản 3 Điều này, ngân hàng thương mại phải tiến hành các thủ tục pháp lý theo quy định của pháp luật để chấm dứt hoạt động của chi nhánh, phòng giao dịch; có văn bản báo cáo Ngân hàng Nhà nước (qua Cơ quan Thanh tra, giám sát ngân hàng) và Ngân hàng Nhà nước chi nhánh nơi đặt trụ sở chi nhánh, phòng giao dịch về ngày chấm dứt hoạt động.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Điều 20</t>
+          <t>Khoản 4 Điều 24</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>43/2020/NĐ-CP</t>
+          <t>21/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162587</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43235</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7371,11 +7352,12 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:eb4c1020-2d45-11f1-aaae-d517cf429e25:2022-01-10</t>
+          <t>vilextime:T2:provision:e653e450-2ab9-11f1-8795-75a5ce3bd467:2025-03-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7385,37 +7367,37 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pháp luật về xử phạt vi phạm hành chính trong chăn nuôi quy định những chức danh Công an cấp cơ sở nào có thẩm quyền xử phạt và đối với hành vi nào?</t>
+          <t>Theo quy định về điều tra tai nạn giao thông đường sắt, Cảnh sát giao thông được tạm giữ những gì liên quan đến phương tiện và người điều khiển phương tiện đường bộ?</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3. Thẩm quyền xử phạt vi phạm hành chính của Công an nhân dân:</t>
+          <t>Điều 15. Một số hoạt động thu thập tài liệu khác liên quan đến vụ tai nạn</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>a) Trưởng Công an cấp xã, Trưởng đồn Công an, Trưởng trạm Công an cửa khẩu, khu chế xuất, Trưởng Công an cửa khẩu Cảng hàng không quốc tế, Thủy đội trưởng xử phạt đối với những hành vi vi phạm hành chính quy định tại khoản 1 Điều 29 Nghị định này;</t>
+          <t>1. Tạm giữ tang vật, phương tiện, giấy phép, chứng chỉ hành nghề của người điều khiển phương tiện đường bộ liên quan đến vụ tai nạn giao thông đường sắt được thực hiện theo quy định tại Điều 125 Luật Xử lý vi phạm hành chính năm 2012 (sửa đổi, bổ sung năm 2020) và các quy định khác có liên quan. Đối với trường hợp các giấy tờ có liên quan đến người và phương tiện giao thông đã được tích hợp trong căn cước điện tử, tài khoản định danh điện tử trên Ứng dụng định danh quốc gia, khi tạm giữ giấy tờ, Cảnh sát giao thông thực hiện việc tạm giữ giấy tờ trên môi trường điện tử. Việc xử lý tang vật, phương tiện, giấy phép, chứng chỉ hành nghề của người điều khiển phương tiện liên quan đến vụ tai nạn giao thông đường sắt được thực hiện theo quy định tại Điều 126 Luật Xử lý vi phạm hành chính năm 2012 (sửa đổi, bổ sung năm 2020) và các quy định khác có liên quan.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 3 Điều 44</t>
+          <t>Khoản 1 Điều 15</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>14/2021/NĐ-CP</t>
+          <t>34/2018/TT-BCA</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148195</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177104</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7435,11 +7417,12 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ec121e20-29f6-11f1-86b5-0d550726534d:2024-02-26</t>
+          <t>vilextime:T2:provision:e902d34e-df52-11f0-b1c8-1baca6cbd210:2021-12-31</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7449,37 +7432,37 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Khi nam sĩ quan mặc trang phục dự lễ mùa đông, áo sơ mi mặc trong có kiểu dáng và cách mặc như thế nào?</t>
+          <t>Thẩm quyền tịch thu tang vật, phương tiện vi phạm hành chính trong lĩnh vực giáo dục của Chủ tịch Ủy ban nhân dân cấp huyện bị giới hạn như thế nào về giá trị?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Điều 9. Trang phục dự lễ mùa đông của nam sĩ quan, quân nhân chuyên nghiệp, học viên là sĩ quan và học viên đào tạo sĩ quan</t>
+          <t>2. Chủ tịch Ủy ban nhân dân huyện, quận, thị xã, thành phố trực thuộc tỉnh (cấp huyện) có quyền:</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>3. Áo sơ mi mặc trong: Kiểu áo buông, mặc bỏ trong quần, dài tay, cổ đứng, mầu trắng.</t>
+          <t>d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt quy định tại điểm b khoản này;</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 9</t>
+          <t>Điểm d Khoản 2 Điều 36</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>82/2016/NĐ-CP</t>
+          <t>04/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112003</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148174</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7494,20 +7477,17 @@
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>Phiên bản 2 bỏ 'mặc bỏ trong quần' và gộp Điều 9 thành 'trang phục dự lễ'</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ec4b5dbe-df43-11f0-980f-9505879c1a66#k1#b:2017-01-31</t>
+          <t>vilextime:T2:provision:e93ccd50-2c83-11f1-bc09-954fa6134772:2023-07-18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7517,37 +7497,37 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Theo quy định về đào tạo nghiệp vụ quản lý vận hành nhà chung cư, sau khi nhận đủ hồ sơ công nhận cơ sở đào tạo thì cơ quan nào kiểm tra và xử lý trong bao lâu?</t>
+          <t>Trường hợp đăng ký một quy chuẩn kỹ thuật đã ban hành, hồ sơ và thủ tục đăng ký được thực hiện theo quy định nào?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1. Trình tự, thủ tục công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư được quy định như sau:</t>
+          <t>Điều 14. Thông báo, phổ biến, đăng ký, xuất bản, phát hành quy chuẩn kỹ thuật</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>b) Trong thời hạn 20 ngày, kể từ ngày nhận được đầy đủ hồ sơ theo quy định tại Điều 5 của Thông tư này, cơ quan được giao tiếp nhận và xử lý hồ sơ có trách nhiệm kiểm tra, nếu đủ điều kiện thì báo cáo Bộ Xây dựng ban hành quyết định công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư. Trong trường hợp cần thiết, cơ quan kiểm tra hồ sơ trực tiếp kiểm tra hoặc đề nghị Sở Xây dựng nơi cơ sở đào tạo dự kiến tổ chức đào tạo kiểm tra các điều kiện theo quy định tại Điều 4 của Thông tư này.</t>
+          <t>4. Hồ sơ, thủ tục đăng ký quy chuẩn kỹ thuật đã ban hành thực hiện theo quy định tại Điều 13 Nghị định số 127/2007/NĐ-CP. Bản đăng ký quy chuẩn kỹ thuật được lập theo Mẫu quy định tại Phụ lục XI kèm theo Thông tư này.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 7</t>
+          <t>Khoản 4 Điều 14</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>10/2015/TT-BXD</t>
+          <t>26/2019/TT-BKHCN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98477</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146540</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7562,16 +7542,21 @@
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Chỗ đổi chính là thêm Mẫu bản đăng ký (Phụ lục XI); căn cứ Điều 13 NĐ 127/2007 giữ nguyên</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ec4b5dbe-df43-11f0-980f-9505879c1a66#k1#b:2017-02-01</t>
+          <t>vilextime:T2:provision:e9b9d5f4-df42-11f0-a5f2-138bc0b82b6b:2025-07-01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7581,37 +7566,37 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Theo quy định về đào tạo nghiệp vụ quản lý vận hành nhà chung cư, sau khi nhận đủ hồ sơ công nhận cơ sở đào tạo thì cơ quan nào kiểm tra và xử lý trong bao lâu?</t>
+          <t>Nếu một địa phương được chọn đặt địa điểm thi hành án tử hình bằng tiêm thuốc độc, thì Ủy ban nhân dân cấp tỉnh có trách nhiệm gì và chỉ đạo chính quyền cấp nào phối hợp?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1. Trình tự, thủ tục công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư được quy định như sau:</t>
+          <t>Mục 3 TRÁCH NHIỆM CỦA CÁC BỘ VÀ ỦY BAN NHÂN DÂN CÁC CẤP TRONG THI HÀNH ÁN TỬ HÌNH</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>b) Trong thời hạn 20 ngày, kể từ ngày nhận được đầy đủ hồ sơ theo quy định tại Điều 5 của Thông tư này, Cục Quản lý nhà và thị trường bất động sản có trách nhiệm kiểm tra hồ sơ, nếu đủ điều kiện theo quy định tại các Khoản 1, 2, 3 và 4 Điều 3 của Nghị định số 79/2016/NĐ-CP thì báo cáo Bộ Xây dựng ban hành quyết định hoặc ủy quyền cho Cục Quản lý nhà và thị trường bất động sản ban hành quyết định công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư. Tên và địa chỉ của cơ sở đào tạo, được Bộ Xây dựng công nhận được thông báo công khai trên Cổng thông tin điện tử của Bộ Xây dựng và của Cục Quản lý nhà và thị trường bất động sản. Sau khi có quyết định công nhận của Bộ Xây dựng, cơ sở đào tạo có trách nhiệm gửi 01 bộ hồ sơ (bản sao) đề nghị công nhận cơ sở đào tạo đã được Bộ Xây dựng chấp thuận cho Sở Xây dựng nơi tổ chức đào tạo để Sở Xây dựng thực hiện theo dõi, kiểm tra và quản lý</t>
+          <t>Điều 20. Trách nhiệm của Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương có trách nhiệm cấp đất để xây dựng địa điểm thi hành án tử hình, chỉ định nơi mai táng người bị thi hành án tử hình; chỉ đạo Ủy ban nhân dân cấp xã, các cơ quan liên quan ở địa phương phối hợp bảo đảm an ninh, trật tự, an toàn cho việc thi hành án tử hình.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 7</t>
+          <t>Điều 20</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>10/2015/TT-BXD</t>
+          <t>43/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98477</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162587</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7631,11 +7616,12 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:edc507d0-df43-11f0-955c-a3b1b5737505#k6:2017-08-15</t>
+          <t>vilextime:T2:provision:eb4c1020-2d45-11f1-aaae-d517cf429e25:2022-01-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7645,37 +7631,37 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pháp luật về quản lý ngoại hối đối với vay nước ngoài quy định yêu cầu nộp văn bản phê duyệt của cấp có thẩm quyền trong hồ sơ đăng ký khoản vay như thế nào?</t>
+          <t>Pháp luật về xử phạt vi phạm hành chính trong chăn nuôi quy định những chức danh Công an cấp cơ sở nào có thẩm quyền xử phạt và đối với hành vi nào?</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Điều 14. Hồ sơ đăng ký khoản vay</t>
+          <t>3. Thẩm quyền xử phạt vi phạm hành chính của Công an nhân dân:</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>6. Bản sao (có xác nhận của Bên đi vay) văn bản của cấp có thẩm quyền phê duyệt việc vay nước ngoài theo quy định của pháp luật về phân công, phân cấp thực hiện các quyền, trách nhiệm, nghĩa vụ của chủ sở hữu nhà nước đối với doanh nghiệp nhà nước và vốn nhà nước đầu tư vào doanh nghiệp đối với Bên đi vay là doanh nghiệp nhà nước, trừ trường hợp Bên đi vay là ngân hàng thương mại do Nhà nước nắm giữ 100% vốn điều lệ.</t>
+          <t>a) Trưởng Công an cấp xã, Trưởng đồn Công an, Trưởng trạm Công an cửa khẩu, khu chế xuất, Trưởng Công an cửa khẩu Cảng hàng không quốc tế, Thủy đội trưởng xử phạt đối với những hành vi vi phạm hành chính quy định tại khoản 1 Điều 29 Nghị định này;</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Khoản 6 Điều 14</t>
+          <t>Điểm a Khoản 3 Điều 44</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>03/2016/TT-NHNN</t>
+          <t>14/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98528</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=148195</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7695,11 +7681,12 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f1320664-2cbb-11f1-999f-03a8c5a71d2a:2025-05-31</t>
+          <t>vilextime:T2:provision:ec121e20-29f6-11f1-86b5-0d550726534d:2024-02-26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7709,37 +7696,37 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Trường hợp một doanh nghiệp nhập khẩu sản phẩm cần dán tem điện tử, những loại sản phẩm nhập khẩu nào do chính doanh nghiệp nhập khẩu thực hiện việc dán tem?</t>
+          <t>Khi nam sĩ quan mặc trang phục dự lễ mùa đông, áo sơ mi mặc trong có kiểu dáng và cách mặc như thế nào?</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4. Đơn vị thực hiện dán tem điện tử</t>
+          <t>Điều 9. Trang phục dự lễ mùa đông của nam sĩ quan, quân nhân chuyên nghiệp, học viên là sĩ quan và học viên đào tạo sĩ quan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>a) Đối với sản phẩm thuốc lá nhập khẩu: Doanh nghiệp, tổ chức nhập khẩu sản phẩm thuốc lá đảm bảo việc dán tem đúng quy định cho sản phẩm thuốc lá tại cơ sở sản xuất ở nước ngoài trước khi nhập khẩu vào thị trường Việt Nam để tiêu thụ.</t>
+          <t>3. Áo sơ mi mặc trong: Kiểu áo buông, mặc bỏ trong quần, dài tay, cổ đứng, mầu trắng.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 4 Điều 3</t>
+          <t>Khoản 3 Điều 9</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>23/2021/TT-BTC</t>
+          <t>82/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150991</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112003</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7749,33 +7736,26 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Ở phiên bản 1, thuốc lá nhập khẩu được dán tem tại cơ sở sản xuất ở nước ngoài; sản phẩm do chính doanh nghiệp nhập khẩu dán tem là rượu (điểm b), không phải điểm a</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>b) Đối với sản phẩm rượu đóng chai và rượu thành phẩm dạng thùng, téc nhập khẩu về sang, chiết ra chai: Doanh...</t>
-        </is>
-      </c>
+          <t>Phiên bản 2 bỏ 'mặc bỏ trong quần' và gộp Điều 9 thành 'trang phục dự lễ'</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f1327b80-2cbb-11f1-8b28-794b164010fc:2025-06-01</t>
+          <t>vilextime:T2:provision:ec4b5dbe-df43-11f0-980f-9505879c1a66#k1#b:2017-01-31</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7785,37 +7765,37 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Việc dán tem điện tử đối với rượu nhập khẩu được sang, chiết ra chai tại Việt Nam được xác định ra sao về đơn vị thực hiện?</t>
+          <t>Theo quy định về đào tạo nghiệp vụ quản lý vận hành nhà chung cư, sau khi nhận đủ hồ sơ công nhận cơ sở đào tạo thì cơ quan nào kiểm tra và xử lý trong bao lâu?</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2017-01-31</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4. Đơn vị thực hiện dán tem điện tử</t>
+          <t>1. Trình tự, thủ tục công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư được quy định như sau:</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>b) Trường hợp doanh nghiệp, tổ chức nhập khẩu sản phẩm rượu đóng chai hoặc nhập khẩu sản phẩm thuốc lá có nhu cầu dán tem điện tử tại cơ sở sản xuất ở nước ngoài thì phải đảm bảo việc dán tem điện tử theo đúng quy định tại Thông tư này trước khi nhập khẩu vào lãnh thổ Việt Nam.</t>
+          <t>b) Trong thời hạn 20 ngày, kể từ ngày nhận được đầy đủ hồ sơ theo quy định tại Điều 5 của Thông tư này, cơ quan được giao tiếp nhận và xử lý hồ sơ có trách nhiệm kiểm tra, nếu đủ điều kiện thì báo cáo Bộ Xây dựng ban hành quyết định công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư. Trong trường hợp cần thiết, cơ quan kiểm tra hồ sơ trực tiếp kiểm tra hoặc đề nghị Sở Xây dựng nơi cơ sở đào tạo dự kiến tổ chức đào tạo kiểm tra các điều kiện theo quy định tại Điều 4 của Thông tư này.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 4 Điều 3</t>
+          <t>Điểm b Khoản 1 Điều 7</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>23/2021/TT-BTC</t>
+          <t>10/2015/TT-BXD</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150991</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98477</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7825,33 +7805,22 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>gold_wrong</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Từ 2025-06-01 điểm b nói về dán tem tại cơ sở sản xuất ở nước ngoài; quy định cho rượu nhập khẩu sang, chiết ra chai chuyển sang điểm a mới (cùng sự kiện sửa đổi event:178308:b8c6a8e03615381904420010)</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>a) Doanh nghiệp, tổ chức nhập khẩu sản phẩm rượu đóng chai, rượu thành phẩm dạng thùng, téc nhập khẩu về sang, chiết ra chai hoặc nhập khẩu sản phẩm thuốc lá có nhu cầu dán tem điện tử trong quá trình làm thủ tục nhập khẩu hoặc sau khi đã hoàn thành thủ tục nhập khẩu thì phải thực hiện dán tem điện tử… và tự chịu trách nhiệm việc dán tem điện tử trước khi đưa ra thị trường tiêu thụ.</t>
-        </is>
-      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f22d30de-e161-11f0-a307-df2e095a6f35:2025-06-30</t>
+          <t>vilextime:T2:provision:ec4b5dbe-df43-11f0-980f-9505879c1a66#k1#b:2017-02-01</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7861,37 +7830,37 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Khi Bộ Công an trang bị phương tiện cho lực lượng bảo vệ an ninh, trật tự ở cơ sở từ ngân sách trung ương, kế hoạch trang bị được lập và gửi theo trình tự nào?</t>
+          <t>Theo quy định về đào tạo nghiệp vụ quản lý vận hành nhà chung cư, sau khi nhận đủ hồ sơ công nhận cơ sở đào tạo thì cơ quan nào kiểm tra và xử lý trong bao lâu?</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2. Lập kế hoạch trang bị, mua sắm phương tiện, thiết bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở:</t>
+          <t>1. Trình tự, thủ tục công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư được quy định như sau:</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>a) Trường hợp Bộ Công an trang bị phương tiện, thiết bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở do ngân sách trung ương bảo đảm theo quy định tại khoản 1 Điều 25 Luật Lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở: Hằng năm, Công an cấp xã tổng hợp nhu cầu phương tiện, thiết bị cần trang bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở gửi Công an cấp huyện báo cáo Công an cấp tỉnh tổng hợp, lập dự trù kinh phí và báo cáo Bộ Công an xem xét, quyết định việc mua sắm, trang bị phù hợp với khả năng ngân sách nhà nước cấp cho Bộ Công an;</t>
+          <t>b) Trong thời hạn 20 ngày, kể từ ngày nhận được đầy đủ hồ sơ theo quy định tại Điều 5 của Thông tư này, Cục Quản lý nhà và thị trường bất động sản có trách nhiệm kiểm tra hồ sơ, nếu đủ điều kiện theo quy định tại các Khoản 1, 2, 3 và 4 Điều 3 của Nghị định số 79/2016/NĐ-CP thì báo cáo Bộ Xây dựng ban hành quyết định hoặc ủy quyền cho Cục Quản lý nhà và thị trường bất động sản ban hành quyết định công nhận cơ sở đủ điều kiện được đào tạo, bồi dưỡng kiến thức chuyên môn, nghiệp vụ quản lý vận hành nhà chung cư. Tên và địa chỉ của cơ sở đào tạo, được Bộ Xây dựng công nhận được thông báo công khai trên Cổng thông tin điện tử của Bộ Xây dựng và của Cục Quản lý nhà và thị trường bất động sản. Sau khi có quyết định công nhận của Bộ Xây dựng, cơ sở đào tạo có trách nhiệm gửi 01 bộ hồ sơ (bản sao) đề nghị công nhận cơ sở đào tạo đã được Bộ Xây dựng chấp thuận cho Sở Xây dựng nơi tổ chức đào tạo để Sở Xây dựng thực hiện theo dõi, kiểm tra và quản lý</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 4</t>
+          <t>Điểm b Khoản 1 Điều 7</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>40/2024/NĐ-CP</t>
+          <t>10/2015/TT-BXD</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168328</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98477</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7911,11 +7880,12 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f29448d2-df4f-11f0-bd54-b3aab7343403:2024-06-30</t>
+          <t>vilextime:T2:provision:edc507d0-df43-11f0-955c-a3b1b5737505#k6:2017-08-15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7925,37 +7895,37 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Theo quy định về chấp thuận nội dung thay đổi của ngân hàng thương mại, thông tư điều chỉnh hồ sơ, thủ tục chấp thuận đối với những loại thay đổi nào?</t>
+          <t>Pháp luật về quản lý ngoại hối đối với vay nước ngoài quy định yêu cầu nộp văn bản phê duyệt của cấp có thẩm quyền trong hồ sơ đăng ký khoản vay như thế nào?</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1. Thông tư này quy định về:</t>
+          <t>Điều 14. Hồ sơ đăng ký khoản vay</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>b) Hồ sơ, trình tự, thủ tục chấp thuận các nội dung thay đổi của ngân hàng thương mại, chi nhánh ngân hàng nước ngoài: (i) Mua bán, chuyển nhượng phần vốn góp của chủ sở hữu ngân hàng thương mại trách nhiệm hữu hạn một thành viên; mua bán, chuyển nhượng phần vốn góp của thành viên góp vốn của ngân hàng thương mại trách nhiệm hữu hạn hai thành viên trở lên; (ii) Mua bán, chuyển nhượng cổ phần của cổ đông lớn; mua bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại; (iii) Tạm ngừng hoạt động kinh doanh từ 05 ngày làm việc trở lên, trừ trường hợp tạm ngừng hoạt động do sự kiện bất khả kháng.</t>
+          <t>6. Bản sao (có xác nhận của Bên đi vay) văn bản của cấp có thẩm quyền phê duyệt việc vay nước ngoài theo quy định của pháp luật về phân công, phân cấp thực hiện các quyền, trách nhiệm, nghĩa vụ của chủ sở hữu nhà nước đối với doanh nghiệp nhà nước và vốn nhà nước đầu tư vào doanh nghiệp đối với Bên đi vay là doanh nghiệp nhà nước, trừ trường hợp Bên đi vay là ngân hàng thương mại do Nhà nước nắm giữ 100% vốn điều lệ.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 1</t>
+          <t>Khoản 6 Điều 14</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>50/2018/TT-NHNN</t>
+          <t>03/2016/TT-NHNN</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98528</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7965,33 +7935,22 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>Điểm a cùng khoản cũng là 'hồ sơ, thủ tục chấp thuận thay đổi' (thay đổi, sửa đổi, bổ sung Giấy phép); câu hỏi 'những loại thay đổi nào' khớp cả điểm a và b</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>a) Hồ sơ, trình tự, thủ tục chấp thuận thay đổi, việc sửa đổi, bổ sung Giấy phép thành lập và hoạt động của ng...</t>
-        </is>
-      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f29448d2-df4f-11f0-bd54-b3aab7343403:2024-07-01</t>
+          <t>vilextime:T2:provision:f1320664-2cbb-11f1-999f-03a8c5a71d2a:2025-05-31</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8001,37 +7960,37 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Theo quy định về chấp thuận nội dung thay đổi của ngân hàng thương mại, thông tư điều chỉnh hồ sơ, thủ tục chấp thuận đối với những loại thay đổi nào?</t>
+          <t>Trường hợp một doanh nghiệp nhập khẩu sản phẩm cần dán tem điện tử, những loại sản phẩm nhập khẩu nào do chính doanh nghiệp nhập khẩu thực hiện việc dán tem?</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1. Thông tư này quy định về:</t>
+          <t>4. Đơn vị thực hiện dán tem điện tử</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>b) Hồ sơ, thủ tục chấp thuận các nội dung thay đổi của ngân hàng thương mại, chi nhánh ngân hàng nước ngoài: (i) Mua bán, chuyển nhượng phần vốn góp của chủ sở hữu ngân hàng thương mại trách nhiệm hữu hạn một thành viên; mua, bán, chuyển nhượng phần vốn góp của thành viên góp vốn của ngân hàng thương mại trách nhiệm hữu hạn hai thành viên trở lên; (ii) Mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại; (iii) Tạm ngừng giao dịch từ 05 ngày làm việc trở lên, trừ trường hợp tạm ngừng giao dịch do sự kiện bất khả kháng.</t>
+          <t>a) Đối với sản phẩm thuốc lá nhập khẩu: Doanh nghiệp, tổ chức nhập khẩu sản phẩm thuốc lá đảm bảo việc dán tem đúng quy định cho sản phẩm thuốc lá tại cơ sở sản xuất ở nước ngoài trước khi nhập khẩu vào thị trường Việt Nam để tiêu thụ.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 1 Điều 1</t>
+          <t>Điểm a Khoản 4 Điều 3</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>50/2018/TT-NHNN</t>
+          <t>23/2021/TT-BTC</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150991</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -8052,22 +8011,27 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Điểm a cùng khoản cũng là 'hồ sơ, thủ tục chấp thuận thay đổi' (thay đổi, sửa đổi, bổ sung Giấy phép); câu hỏi 'những loại thay đổi nào' khớp cả điểm a và b</t>
+          <t>Ở phiên bản 1, thuốc lá nhập khẩu được dán tem tại cơ sở sản xuất ở nước ngoài; sản phẩm do chính doanh nghiệp nhập khẩu dán tem là rượu (điểm b), không phải điểm a</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>a) Hồ sơ, trình tự, thủ tục chấp thuận thay đổi, việc sửa đổi, bổ sung Giấy phép thành lập và hoạt động của ng...</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr"/>
+          <t>b) Đối với sản phẩm rượu đóng chai và rượu thành phẩm dạng thùng, téc nhập khẩu về sang, chiết ra chai: Doanh...</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Ở phiên bản 1, thuốc lá nhập khẩu được dán tem tại cơ sở sản xuất ở nước ngoài; sản phẩm do chính doanh nghiệp nhập khẩu dán tem là rượu (điểm b), không phải điểm a</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f3c5a718-eb76-11f0-8093-2da175569ed4#k3:1998-10-10</t>
+          <t>vilextime:T2:provision:f1327b80-2cbb-11f1-8b28-794b164010fc:2025-06-01</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8077,37 +8041,37 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pháp luật về xử phạt vi phạm trật tự an toàn giao thông đường bộ và đô thị quy định việc xử phạt người điều khiển xe lam, xe công nông và các loại xe tương tự như thế nào?</t>
+          <t>Việc dán tem điện tử đối với rượu nhập khẩu được sang, chiết ra chai tại Việt Nam được xác định ra sao về đơn vị thực hiện?</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1998-10-10</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Điều 15:</t>
+          <t>4. Đơn vị thực hiện dán tem điện tử</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>3. Người điều khiển xe lam, xe công nông, xe bông sen và những loại xe có tiêu chuẩn kỹ thuật tương tự có hành vi quy định tại Điều 13 và Điều 14 của Nghị định này thì bị xử phạt theo các quy định tại điều đó.</t>
+          <t>b) Trường hợp doanh nghiệp, tổ chức nhập khẩu sản phẩm rượu đóng chai hoặc nhập khẩu sản phẩm thuốc lá có nhu cầu dán tem điện tử tại cơ sở sản xuất ở nước ngoài thì phải đảm bảo việc dán tem điện tử theo đúng quy định tại Thông tư này trước khi nhập khẩu vào lãnh thổ Việt Nam.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 15</t>
+          <t>Điểm b Khoản 4 Điều 3</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>49/CP</t>
+          <t>23/2021/TT-BTC</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9725</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150991</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -8122,28 +8086,33 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>question_ambiguous</t>
+          <t>gold_wrong</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Khoản 1, 2 cùng Điều 15 đặt mức phạt trực tiếp cho người điều khiển xe lam (100.000 đồng) và xe công nông, bông sen (500.000 đồng); câu hỏi chung 'xử phạt như thế nào' khớp cả ba khoản</t>
+          <t>Từ 2025-06-01 điểm b nói về dán tem tại cơ sở sản xuất ở nước ngoài; quy định cho rượu nhập khẩu sang, chiết ra chai chuyển sang điểm a mới (cùng sự kiện sửa đổi event:178308:b8c6a8e03615381904420010)</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>1. Phạt 100.000 đồng đối với người điều khiển xe lam có một trong các hành vi sau đây... | 2. Phạt tiền 500.000 đồng đối với người điều khiển xe công nông, xe bông sen...</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr"/>
+          <t>a) Doanh nghiệp, tổ chức nhập khẩu sản phẩm rượu đóng chai, rượu thành phẩm dạng thùng, téc nhập khẩu về sang, chiết ra chai hoặc nhập khẩu sản phẩm thuốc lá có nhu cầu dán tem điện tử trong quá trình làm thủ tục nhập khẩu hoặc sau khi đã hoàn thành thủ tục nhập khẩu thì phải thực hiện dán tem điện tử… và tự chịu trách nhiệm việc dán tem điện tử trước khi đưa ra thị trường tiêu thụ.</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>loại lineage (gold_wrong): Từ 2025-06-01 điểm b nói về dán tem tại cơ sở sản xuất ở nước ngoài; quy định cho rượu nhập khẩu sang, chiết ra chai chuyển sang điểm a mới (cùng sự kiện sửa đổi event:178308:b8c6a8e03615381904420010)</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f3c5a718-eb76-11f0-8093-2da175569ed4#k3:1998-10-11</t>
+          <t>vilextime:T2:provision:f22d30de-e161-11f0-a307-df2e095a6f35:2025-06-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8153,37 +8122,37 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pháp luật về xử phạt vi phạm trật tự an toàn giao thông đường bộ và đô thị quy định việc xử phạt người điều khiển xe lam, xe công nông và các loại xe tương tự như thế nào?</t>
+          <t>Khi Bộ Công an trang bị phương tiện cho lực lượng bảo vệ an ninh, trật tự ở cơ sở từ ngân sách trung ương, kế hoạch trang bị được lập và gửi theo trình tự nào?</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1998-10-11</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Điều 15:</t>
+          <t>2. Lập kế hoạch trang bị, mua sắm phương tiện, thiết bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở:</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>3. Người điều khiển xe lam, xe "Công nông", xe "Bông sen" và những loại xe có tiêu chuẩn kỹ thuật tương tự vi phạm các quy định tại các Điều 13, 14, 17 của Nghị định này thì bị xử phạt theo các quy định tại những điều đó.</t>
+          <t>a) Trường hợp Bộ Công an trang bị phương tiện, thiết bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở do ngân sách trung ương bảo đảm theo quy định tại khoản 1 Điều 25 Luật Lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở: Hằng năm, Công an cấp xã tổng hợp nhu cầu phương tiện, thiết bị cần trang bị cho lực lượng tham gia bảo vệ an ninh, trật tự ở cơ sở gửi Công an cấp huyện báo cáo Công an cấp tỉnh tổng hợp, lập dự trù kinh phí và báo cáo Bộ Công an xem xét, quyết định việc mua sắm, trang bị phù hợp với khả năng ngân sách nhà nước cấp cho Bộ Công an;</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 15</t>
+          <t>Điểm a Khoản 2 Điều 4</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>49/CP</t>
+          <t>40/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9725</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168328</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -8193,33 +8162,22 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>Khoản 1, 2 cùng Điều 15 đặt mức phạt trực tiếp cho người điều khiển xe lam (100.000 đồng) và xe công nông, bông sen (500.000 đồng); câu hỏi chung 'xử phạt như thế nào' khớp cả ba khoản</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>1. Phạt 100.000 đồng đối với người điều khiển xe lam có một trong các hành vi sau đây... | 2. Phạt tiền 500.000 đồng đối với người điều khiển xe công nông, xe bông sen...</t>
-        </is>
-      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f5c84a38-df38-11f0-9573-ffc15f872947:2024-12-11</t>
+          <t>vilextime:T2:provision:f29448d2-df4f-11f0-bd54-b3aab7343403:2024-06-30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8229,37 +8187,37 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Một Trạm Thú y sau khi nhận thông báo dịch bệnh thủy sản và tổ chức giám sát thì phải báo cáo kết quả thực hiện cho cơ quan nào?</t>
+          <t>Ngoài việc sửa đổi, bổ sung Giấy phép, thông tư quy định hồ sơ, thủ tục chấp thuận đối với những nội dung thay đổi nào khác của ngân hàng thương mại?</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:</t>
+          <t>1. Thông tư này quy định về:</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>c) Báo cáo Chi cục Thú y kết quả thực hiện.</t>
+          <t>b) Hồ sơ, trình tự, thủ tục chấp thuận các nội dung thay đổi của ngân hàng thương mại, chi nhánh ngân hàng nước ngoài: (i) Mua bán, chuyển nhượng phần vốn góp của chủ sở hữu ngân hàng thương mại trách nhiệm hữu hạn một thành viên; mua bán, chuyển nhượng phần vốn góp của thành viên góp vốn của ngân hàng thương mại trách nhiệm hữu hạn hai thành viên trở lên; (ii) Mua bán, chuyển nhượng cổ phần của cổ đông lớn; mua bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại; (iii) Tạm ngừng hoạt động kinh doanh từ 05 ngày làm việc trở lên, trừ trường hợp tạm ngừng hoạt động do sự kiện bất khả kháng.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 2 Điều 16</t>
+          <t>Điểm b Khoản 1 Điều 1</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>04/2016/TT-BNNPTNT</t>
+          <t>50/2018/TT-NHNN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -8276,18 +8234,19 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Phiên bản 2 gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện' (câu dẫn)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về chấp thuận nội dung thay đổi của ngân hàng thương mại, thông tư điều chỉnh hồ sơ, thủ tục chấp thuận đối với những loại thay đổi nào?»; nhãn cũ khong_dat question_ambiguous: Điểm a cùng khoản cũng là 'hồ sơ, thủ tục chấp thuận thay đổi' (thay đổi, sửa đổi, bổ sung Giấy phép); câu hỏi 'những loại thay đổi nào' khớp cả điểm a và b). Câu hỏi loại điểm a (sửa đổi, bổ sung Giấy phép)</t>
         </is>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f714afba-2c06-11f1-9451-d978a915fbc0:1999-01-01</t>
+          <t>vilextime:T2:provision:f29448d2-df4f-11f0-bd54-b3aab7343403:2024-07-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8297,37 +8256,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Theo quy định về phân cấp, lập và chấp hành ngân sách nhà nước, cơ quan thuế địa phương khi lập dự toán thu ngân sách trên địa bàn phải dự kiến những khoản gì và gửi cho những cơ quan nào?</t>
+          <t>Ngoài việc sửa đổi, bổ sung Giấy phép, thông tư quy định hồ sơ, thủ tục chấp thuận đối với những nội dung thay đổi nào khác của ngân hàng thương mại?</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Điều 34.</t>
+          <t>1. Thông tư này quy định về:</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2. Cơ quan thuế ở địa phương lập dự toán thu ngân sách nhà nước trên địa bàn, dự kiến số thuế giá trị gia tăng phải hoàn cho các doanh nghiệp trên địa bàn thuộc phạm vi quản lý gửi cơ quan thuế cấp trên, Uỷ ban nhân dân, cơ quan tài chính, cơ quan kế hoạch và đầu tư cùng cấp.</t>
+          <t>b) Hồ sơ, thủ tục chấp thuận các nội dung thay đổi của ngân hàng thương mại, chi nhánh ngân hàng nước ngoài: (i) Mua bán, chuyển nhượng phần vốn góp của chủ sở hữu ngân hàng thương mại trách nhiệm hữu hạn một thành viên; mua, bán, chuyển nhượng phần vốn góp của thành viên góp vốn của ngân hàng thương mại trách nhiệm hữu hạn hai thành viên trở lên; (ii) Mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại; (iii) Tạm ngừng giao dịch từ 05 ngày làm việc trở lên, trừ trường hợp tạm ngừng giao dịch do sự kiện bất khả kháng.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 34</t>
+          <t>Điểm b Khoản 1 Điều 1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>87-CP</t>
+          <t>50/2018/TT-NHNN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8885</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -8342,16 +8301,21 @@
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Theo quy định về chấp thuận nội dung thay đổi của ngân hàng thương mại, thông tư điều chỉnh hồ sơ, thủ tục chấp thuận đối với những loại thay đổi nào?»; nhãn cũ khong_dat question_ambiguous: Điểm a cùng khoản cũng là 'hồ sơ, thủ tục chấp thuận thay đổi' (thay đổi, sửa đổi, bổ sung Giấy phép); câu hỏi 'những loại thay đổi nào' khớp cả điểm a và b). Câu hỏi loại điểm a (sửa đổi, bổ sung Giấy phép)</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f78365e0-1df6-11f1-a27b-2bd2862aefdb:2023-11-26</t>
+          <t>vilextime:T2:provision:f3c5a718-eb76-11f0-8093-2da175569ed4#k3:1998-10-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8361,37 +8325,37 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Theo quy định về cơ sở đào tạo, huấn luyện thuyền viên hàng hải, văn bản đề nghị cấp lại Giấy chứng nhận được nộp đến cơ quan nào và bằng những hình thức nào?</t>
+          <t>Người điều khiển xe lam, xe công nông, xe bông sen có hành vi vi phạm thuộc các điều khác của nghị định thì bị xử phạt theo những điều nào?</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>1998-10-10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Điều 8. Cấp lại Giấy chứng nhận</t>
+          <t>Điều 15:</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2. Cơ sở đào tạo, huấn luyện nộp trực tiếp hoặc gửi bằng hình thức phù hợp khác đến Bộ Giao thông vận tải văn bản đề nghị cấp lại Giấy chứng nhận, trong đó nêu rõ lý do cấp lại kèm theo các tài liệu chứng minh sự thay đổi thông tin về cơ sở đào tạo (nếu có). Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị, Bộ Giao thông vận tải cấp lại Giấy chứng nhận; trường hợp không cấp lại phải có văn bản trả lời và nêu rõ lý do.</t>
+          <t>3. Người điều khiển xe lam, xe công nông, xe bông sen và những loại xe có tiêu chuẩn kỹ thuật tương tự có hành vi quy định tại Điều 13 và Điều 14 của Nghị định này thì bị xử phạt theo các quy định tại điều đó.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 8</t>
+          <t>Khoản 3 Điều 15</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>29/2017/NĐ-CP</t>
+          <t>49/CP</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120772</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9725</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8406,16 +8370,21 @@
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xử phạt vi phạm trật tự an toàn giao thông đường bộ và đô thị quy định việc xử phạt người điều khiển xe lam, xe công nông và các loại xe tương tự như thế nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 1, 2 cùng Điều 15 đặt mức phạt trực tiếp cho người điều khiển xe lam (100.000 đồng) và xe công nông, bông sen (500.000 đồng); câu hỏi chung 'xử phạt như thế nào' khớp cả ba khoản). Câu hỏi hỏi các điều dẫn chiếu, chỉ khớp khoản 3</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f9f7f0a0-2d52-11f1-b0dd-ff5e5d794920:2024-03-19</t>
+          <t>vilextime:T2:provision:f3c5a718-eb76-11f0-8093-2da175569ed4#k3:1998-10-11</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8425,37 +8394,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nếu một đăng kiểm viên phương tiện thủy nội địa được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?</t>
+          <t>Người điều khiển xe lam, xe công nông, xe bông sen có hành vi vi phạm thuộc các điều khác của nghị định thì bị xử phạt theo những điều nào?</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>1998-10-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2. Phạm vi thực hiện</t>
+          <t>Điều 15:</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>a) Thực hiện công tác kiểm tra đối với các loại phương tiện thủy nội địa (trừ tàu hàng có trọng tải toàn phần từ 2000 tấn trở lên; tàu dầu loại II có trọng tải toàn phần từ 1000 tấn trở lên, tàu dầu loại I có trọng tải toàn phần từ 500 tấn trở lên, tàu hàng cấp VR-SB có trọng tải toàn phần từ 500 tấn trở lên hoặc tàu khách cấp VR-SB có sức chở từ 50 người trở lên, tàu đệm khí, tàu chở hóa chất nguy hiểm, tàu chở khí hóa lỏng);</t>
+          <t>3. Người điều khiển xe lam, xe "Công nông", xe "Bông sen" và những loại xe có tiêu chuẩn kỹ thuật tương tự vi phạm các quy định tại các Điều 13, 14, 17 của Nghị định này thì bị xử phạt theo các quy định tại những điều đó.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 12</t>
+          <t>Khoản 3 Điều 15</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>49/2015/TT-BGTVT</t>
+          <t>49/CP</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86490</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9725</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8465,33 +8434,26 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Thông tư có ba Điều 11, 12, 13 cho đăng kiểm viên hạng III, II, I, mỗi Điều có khoản 'Phạm vi thực hiện' với danh sách tàu loại trừ khác nhau; câu hỏi không nêu hạng</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Điều 11/13: Nhiệm vụ, phạm vi thực hiện của Đăng kiểm viên thực hiện công tác kiểm tra hạng III/hạng I</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về xử phạt vi phạm trật tự an toàn giao thông đường bộ và đô thị quy định việc xử phạt người điều khiển xe lam, xe công nông và các loại xe tương tự như thế nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 1, 2 cùng Điều 15 đặt mức phạt trực tiếp cho người điều khiển xe lam (100.000 đồng) và xe công nông, bông sen (500.000 đồng); câu hỏi chung 'xử phạt như thế nào' khớp cả ba khoản). Câu hỏi hỏi các điều dẫn chiếu, chỉ khớp khoản 3</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:f9f7f0a0-2d52-11f1-b0dd-ff5e5d794920:2024-03-20</t>
+          <t>vilextime:T2:provision:f5c84a38-df38-11f0-9573-ffc15f872947:2024-12-11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8501,37 +8463,37 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nếu một đăng kiểm viên phương tiện thủy nội địa được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?</t>
+          <t>Một Trạm Thú y sau khi nhận thông báo dịch bệnh thủy sản và tổ chức giám sát thì phải báo cáo kết quả thực hiện cho cơ quan nào?</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2. Phạm vi thực hiện</t>
+          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>a) Thực hiện nhiệm vụ theo quy định tại khoản 1 Điều này theo chuyên ngành đào tạo đối với các loại phương tiện thủy nội địa (trừ tàu dầu có tổng dung tích từ 3000 GT trở lên, tàu hàng cấp VR-SB có tổng dung tích từ 3000 GT trở lên hoặc tàu khách cấp VR-SB có sức chở từ 100 người trở lên, tàu chở hóa chất nguy hiểm, tàu chở khí hóa lỏng, tàu chở hàng nguy hiểm);</t>
+          <t>c) Báo cáo Chi cục Thú y kết quả thực hiện.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 12</t>
+          <t>Điểm c Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>49/2015/TT-BGTVT</t>
+          <t>04/2016/TT-BNNPTNT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86490</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8541,33 +8503,26 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Thông tư có ba Điều 11, 12, 13 cho đăng kiểm viên hạng III, II, I, mỗi Điều có khoản 'Phạm vi thực hiện' với danh sách tàu loại trừ khác nhau; câu hỏi không nêu hạng</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Điều 11/13: Nhiệm vụ, phạm vi thực hiện của Đăng kiểm viên thực hiện công tác kiểm tra hạng III/hạng I</t>
-        </is>
-      </c>
+          <t>Phiên bản 2 gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện' (câu dẫn)</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:fb088b5a-df49-11f0-ade8-1187077474c5#k1#n:2018-01-14</t>
+          <t>vilextime:T2:provision:f714afba-2c06-11f1-9451-d978a915fbc0:1999-01-01</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8577,37 +8532,37 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Khi thiết lập các khu vực hạn chế tại cảng hàng không, khu vực liên quan đến soi chiếu hành lý ký gửi được xác định trong phạm vi nào?</t>
+          <t>Theo quy định về phân cấp, lập và chấp hành ngân sách nhà nước, cơ quan thuế địa phương khi lập dự toán thu ngân sách trên địa bàn phải dự kiến những khoản gì và gửi cho những cơ quan nào?</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2018-01-14</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1. Căn cứ thực tế cơ sở hạ tầng và hoạt động hàng không dân dụng, các khu vực hạn chế sau đây phải được thiết lập:</t>
+          <t>Điều 34.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>n) Khu vực từ quầy làm thủ tục, băng chuyền hành lý vào bên trong khu vực soi chiếu hành lý ký gửi;</t>
+          <t>2. Cơ quan thuế ở địa phương lập dự toán thu ngân sách nhà nước trên địa bàn, dự kiến số thuế giá trị gia tăng phải hoàn cho các doanh nghiệp trên địa bàn thuộc phạm vi quản lý gửi cơ quan thuế cấp trên, Uỷ ban nhân dân, cơ quan tài chính, cơ quan kế hoạch và đầu tư cùng cấp.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Điểm n Khoản 1 Điều 34</t>
+          <t>Khoản 2 Điều 34</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01/2016/TT-BGTVT</t>
+          <t>87-CP</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111576</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8885</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8622,20 +8577,17 @@
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>Điểm c (khu vực phân loại hành lý ký gửi sau soi chiếu) gần nghĩa nhưng không nói về soi chiếu; audit xem có cần nêu rõ hơn</t>
-        </is>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ff523980-2c84-11f1-bd91-2d6baf038262:2025-05-18</t>
+          <t>vilextime:T2:provision:f78365e0-1df6-11f1-a27b-2bd2862aefdb:2023-11-26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8645,37 +8597,37 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Trường hợp nhà đầu tư nước ngoài mua cổ phần của một tổ chức tín dụng Việt Nam, tổ chức tín dụng đó có trách nhiệm báo cáo cơ quan có thẩm quyền về những thông tin nào?</t>
+          <t>Theo quy định về cơ sở đào tạo, huấn luyện thuyền viên hàng hải, văn bản đề nghị cấp lại Giấy chứng nhận được nộp đến cơ quan nào và bằng những hình thức nào?</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Điều 16. Trách nhiệm của tổ chức tín dụng Việt Nam</t>
+          <t>Điều 8. Cấp lại Giấy chứng nhận</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>3. Báo cáo đầy đủ, kịp thời cho các cơ quan có thẩm quyền về các thông tin liên quan đến việc nhà đầu tư nước ngoài mua cổ phần.</t>
+          <t>2. Cơ sở đào tạo, huấn luyện nộp trực tiếp hoặc gửi bằng hình thức phù hợp khác đến Bộ Giao thông vận tải văn bản đề nghị cấp lại Giấy chứng nhận, trong đó nêu rõ lý do cấp lại kèm theo các tài liệu chứng minh sự thay đổi thông tin về cơ sở đào tạo (nếu có). Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị, Bộ Giao thông vận tải cấp lại Giấy chứng nhận; trường hợp không cấp lại phải có văn bản trả lời và nêu rõ lý do.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 16</t>
+          <t>Khoản 2 Điều 8</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01/2014/NĐ-CP</t>
+          <t>29/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32937</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120772</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8685,29 +8637,22 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>Câu hỏi đặt trường hợp nhà đầu tư nước ngoài mua cổ phần; với trường hợp đó hai phiên bản trả lời như nhau. Chỗ đổi (thêm tổ chức kinh tế tại khoản 2 Điều 1) câu hỏi không chạm tới</t>
-        </is>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>vilextime:T2:provision:ff523980-2c84-11f1-bd91-2d6baf038262:2025-05-19</t>
+          <t>vilextime:T2:provision:f9f7f0a0-2d52-11f1-b0dd-ff5e5d794920:2024-03-19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8717,37 +8662,37 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Trường hợp nhà đầu tư nước ngoài mua cổ phần của một tổ chức tín dụng Việt Nam, tổ chức tín dụng đó có trách nhiệm báo cáo cơ quan có thẩm quyền về những thông tin nào?</t>
+          <t>Nếu một đăng kiểm viên phương tiện thủy nội địa hạng II được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Điều 16. Trách nhiệm của tổ chức tín dụng Việt Nam</t>
+          <t>2. Phạm vi thực hiện</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>3. Báo cáo đầy đủ, kịp thời cho các cơ quan có thẩm quyền về các thông tin liên quan đến việc nhà đầu tư nước ngoài, tổ chức kinh tế quy định tại khoản 2 Điều 1 Nghị định này mua cổ phần.</t>
+          <t>a) Thực hiện công tác kiểm tra đối với các loại phương tiện thủy nội địa (trừ tàu hàng có trọng tải toàn phần từ 2000 tấn trở lên; tàu dầu loại II có trọng tải toàn phần từ 1000 tấn trở lên, tàu dầu loại I có trọng tải toàn phần từ 500 tấn trở lên, tàu hàng cấp VR-SB có trọng tải toàn phần từ 500 tấn trở lên hoặc tàu khách cấp VR-SB có sức chở từ 50 người trở lên, tàu đệm khí, tàu chở hóa chất nguy hiểm, tàu chở khí hóa lỏng);</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 16</t>
+          <t>Điểm a Khoản 2 Điều 12</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01/2014/NĐ-CP</t>
+          <t>49/2015/TT-BGTVT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32937</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86490</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8757,24 +8702,297 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Câu hỏi đặt trường hợp nhà đầu tư nước ngoài mua cổ phần; với trường hợp đó hai phiên bản trả lời như nhau. Chỗ đổi (thêm tổ chức kinh tế tại khoản 2 Điều 1) câu hỏi không chạm tới</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một đăng kiểm viên phương tiện thủy nội địa được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?»; nhãn cũ khong_dat question_ambiguous: Thông tư có ba Điều 11, 12, 13 cho đăng kiểm viên hạng III, II, I, mỗi Điều có khoản 'Phạm vi thực hiện' với danh sách tàu loại trừ khác nhau; câu hỏi không nêu hạng). Đã nêu hạng II (Điều 12)</t>
         </is>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>vilextime:T2:provision:f9f7f0a0-2d52-11f1-b0dd-ff5e5d794920:2024-03-20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Nếu một đăng kiểm viên phương tiện thủy nội địa hạng II được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2. Phạm vi thực hiện</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>a) Thực hiện nhiệm vụ theo quy định tại khoản 1 Điều này theo chuyên ngành đào tạo đối với các loại phương tiện thủy nội địa (trừ tàu dầu có tổng dung tích từ 3000 GT trở lên, tàu hàng cấp VR-SB có tổng dung tích từ 3000 GT trở lên hoặc tàu khách cấp VR-SB có sức chở từ 100 người trở lên, tàu chở hóa chất nguy hiểm, tàu chở khí hóa lỏng, tàu chở hàng nguy hiểm);</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 12</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>49/2015/TT-BGTVT</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86490</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một đăng kiểm viên phương tiện thủy nội địa được giao kiểm tra phương tiện, thì phạm vi các loại phương tiện mà đăng kiểm viên được thực hiện bị loại trừ những tàu nào?»; nhãn cũ khong_dat question_ambiguous: Thông tư có ba Điều 11, 12, 13 cho đăng kiểm viên hạng III, II, I, mỗi Điều có khoản 'Phạm vi thực hiện' với danh sách tàu loại trừ khác nhau; câu hỏi không nêu hạng). Đã nêu hạng II (Điều 12)</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>vilextime:T2:provision:fb088b5a-df49-11f0-ade8-1187077474c5#k1#n:2018-01-14</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Khi thiết lập các khu vực hạn chế tại cảng hàng không, khu vực liên quan đến soi chiếu hành lý ký gửi được xác định trong phạm vi nào?</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2018-01-14</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1. Căn cứ thực tế cơ sở hạ tầng và hoạt động hàng không dân dụng, các khu vực hạn chế sau đây phải được thiết lập:</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>n) Khu vực từ quầy làm thủ tục, băng chuyền hành lý vào bên trong khu vực soi chiếu hành lý ký gửi;</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Điểm n Khoản 1 Điều 34</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>01/2016/TT-BGTVT</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111576</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Điểm c (khu vực phân loại hành lý ký gửi sau soi chiếu) gần nghĩa nhưng không nói về soi chiếu; audit xem có cần nêu rõ hơn</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>vilextime:T2:provision:ff523980-2c84-11f1-bd91-2d6baf038262:2025-05-18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tổ chức tín dụng Việt Nam phải báo cáo cơ quan có thẩm quyền về thông tin liên quan đến việc mua cổ phần của những đối tượng nào?</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Điều 16. Trách nhiệm của tổ chức tín dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>3. Báo cáo đầy đủ, kịp thời cho các cơ quan có thẩm quyền về các thông tin liên quan đến việc nhà đầu tư nước ngoài mua cổ phần.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Khoản 3 Điều 16</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01/2014/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32937</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp nhà đầu tư nước ngoài mua cổ phần của một tổ chức tín dụng Việt Nam, tổ chức tín dụng đó có trách nhiệm báo cáo cơ quan có thẩm quyền về những thông tin nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi đặt trường hợp nhà đầu tư nước ngoài mua cổ phần; với trường hợp đó hai phiên bản trả lời như nhau. Chỗ đổi (thêm tổ chức kinh tế tại khoản 2 Điều 1) câu hỏi không chạm tới). Câu hỏi hỏi đối tượng mua cổ phần, chính là chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>vilextime:T2:provision:ff523980-2c84-11f1-bd91-2d6baf038262:2025-05-19</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tổ chức tín dụng Việt Nam phải báo cáo cơ quan có thẩm quyền về thông tin liên quan đến việc mua cổ phần của những đối tượng nào?</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Điều 16. Trách nhiệm của tổ chức tín dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3. Báo cáo đầy đủ, kịp thời cho các cơ quan có thẩm quyền về các thông tin liên quan đến việc nhà đầu tư nước ngoài, tổ chức kinh tế quy định tại khoản 2 Điều 1 Nghị định này mua cổ phần.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Khoản 3 Điều 16</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>01/2014/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32937</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp nhà đầu tư nước ngoài mua cổ phần của một tổ chức tín dụng Việt Nam, tổ chức tín dụng đó có trách nhiệm báo cáo cơ quan có thẩm quyền về những thông tin nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi đặt trường hợp nhà đầu tư nước ngoài mua cổ phần; với trường hợp đó hai phiên bản trả lời như nhau. Chỗ đổi (thêm tổ chức kinh tế tại khoản 2 Điều 1) câu hỏi không chạm tới). Câu hỏi hỏi đối tượng mua cổ phần, chính là chỗ đổi</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
